--- a/data/log_analysis_tracker.xlsx
+++ b/data/log_analysis_tracker.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DR25"/>
+  <dimension ref="A1:DS25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,605 +436,610 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>analysis_results_20260203</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>analysis_results_20260201</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20260129</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20260127</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20260125</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20260122</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20260120</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20260118</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20260115</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20260113</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20260111</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20260108</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20260106</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20260104</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20260101</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20251230</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20251228</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20251225</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20251223</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20251221</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20251218</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20251216</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20251214</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20251211</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20251209</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20251207</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20251204</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20251202</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20251130</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20251127</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20251125</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20251123</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20251120</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20251118</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20251116</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20251113</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20251111</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20251109</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20251106</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20251104</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20251102</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20251030</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20251028</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20251026</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20251023</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20251021</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20251019</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20251016</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20251014</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20251012</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20251009</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20251007</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20251005</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20251002</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250930</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250928</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250925</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250923</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250921</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250918</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250916</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250914</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250911</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250909</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250907</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250904</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250902</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250831</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250828</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250826</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250824</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250821</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250819</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250817</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250814</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250812</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250810</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250807</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250805</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250803</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250731</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250729</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250727</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250724</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250722</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250720</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250717</t>
         </is>
       </c>
-      <c r="CJ1" s="1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250715</t>
         </is>
       </c>
-      <c r="CK1" s="1" t="inlineStr">
+      <c r="CL1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250713</t>
         </is>
       </c>
-      <c r="CL1" s="1" t="inlineStr">
+      <c r="CM1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250710</t>
         </is>
       </c>
-      <c r="CM1" s="1" t="inlineStr">
+      <c r="CN1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250708</t>
         </is>
       </c>
-      <c r="CN1" s="1" t="inlineStr">
+      <c r="CO1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250706</t>
         </is>
       </c>
-      <c r="CO1" s="1" t="inlineStr">
+      <c r="CP1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250703</t>
         </is>
       </c>
-      <c r="CP1" s="1" t="inlineStr">
+      <c r="CQ1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250701</t>
         </is>
       </c>
-      <c r="CQ1" s="1" t="inlineStr">
+      <c r="CR1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250629</t>
         </is>
       </c>
-      <c r="CR1" s="1" t="inlineStr">
+      <c r="CS1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250626</t>
         </is>
       </c>
-      <c r="CS1" s="1" t="inlineStr">
+      <c r="CT1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250624</t>
         </is>
       </c>
-      <c r="CT1" s="1" t="inlineStr">
+      <c r="CU1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250622</t>
         </is>
       </c>
-      <c r="CU1" s="1" t="inlineStr">
+      <c r="CV1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250619</t>
         </is>
       </c>
-      <c r="CV1" s="1" t="inlineStr">
+      <c r="CW1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250617</t>
         </is>
       </c>
-      <c r="CW1" s="1" t="inlineStr">
+      <c r="CX1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250615</t>
         </is>
       </c>
-      <c r="CX1" s="1" t="inlineStr">
+      <c r="CY1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250612</t>
         </is>
       </c>
-      <c r="CY1" s="1" t="inlineStr">
+      <c r="CZ1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250610</t>
         </is>
       </c>
-      <c r="CZ1" s="1" t="inlineStr">
+      <c r="DA1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250608</t>
         </is>
       </c>
-      <c r="DA1" s="1" t="inlineStr">
+      <c r="DB1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250605</t>
         </is>
       </c>
-      <c r="DB1" s="1" t="inlineStr">
+      <c r="DC1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250603</t>
         </is>
       </c>
-      <c r="DC1" s="1" t="inlineStr">
+      <c r="DD1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250601</t>
         </is>
       </c>
-      <c r="DD1" s="1" t="inlineStr">
+      <c r="DE1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250529</t>
         </is>
       </c>
-      <c r="DE1" s="1" t="inlineStr">
+      <c r="DF1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250527</t>
         </is>
       </c>
-      <c r="DF1" s="1" t="inlineStr">
+      <c r="DG1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250525</t>
         </is>
       </c>
-      <c r="DG1" s="1" t="inlineStr">
+      <c r="DH1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250522</t>
         </is>
       </c>
-      <c r="DH1" s="1" t="inlineStr">
+      <c r="DI1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250520</t>
         </is>
       </c>
-      <c r="DI1" s="1" t="inlineStr">
+      <c r="DJ1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250518</t>
         </is>
       </c>
-      <c r="DJ1" s="1" t="inlineStr">
+      <c r="DK1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250515</t>
         </is>
       </c>
-      <c r="DK1" s="1" t="inlineStr">
+      <c r="DL1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250513</t>
         </is>
       </c>
-      <c r="DL1" s="1" t="inlineStr">
+      <c r="DM1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250511</t>
         </is>
       </c>
-      <c r="DM1" s="1" t="inlineStr">
+      <c r="DN1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250508</t>
         </is>
       </c>
-      <c r="DN1" s="1" t="inlineStr">
+      <c r="DO1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250506</t>
         </is>
       </c>
-      <c r="DO1" s="1" t="inlineStr">
+      <c r="DP1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250505</t>
         </is>
       </c>
-      <c r="DP1" s="1" t="inlineStr">
+      <c r="DQ1" s="1" t="inlineStr">
         <is>
           <t>project</t>
         </is>
       </c>
-      <c r="DQ1" s="1" t="inlineStr">
+      <c r="DR1" s="1" t="inlineStr">
         <is>
           <t>department</t>
         </is>
       </c>
-      <c r="DR1" s="1" t="inlineStr">
+      <c r="DS1" s="1" t="inlineStr">
         <is>
           <t>job_name</t>
         </is>
@@ -1048,7 +1053,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1083,12 +1088,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1098,7 +1103,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -1108,7 +1113,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -1123,12 +1128,12 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -1198,12 +1203,12 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
@@ -1223,12 +1228,12 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
@@ -1238,17 +1243,17 @@
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -1258,17 +1263,17 @@
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1293,12 +1298,12 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
@@ -1333,12 +1338,12 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1358,7 +1363,7 @@
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
@@ -1368,17 +1373,17 @@
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1403,7 +1408,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1413,12 +1418,12 @@
       </c>
       <c r="BW2" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
@@ -1428,27 +1433,27 @@
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1458,12 +1463,12 @@
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1478,12 +1483,12 @@
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
@@ -1498,12 +1503,12 @@
       </c>
       <c r="CN2" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CO2" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CP2" t="inlineStr">
@@ -1568,27 +1573,27 @@
       </c>
       <c r="DB2" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DC2" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DD2" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DE2" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DF2" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DG2" t="inlineStr">
@@ -1608,7 +1613,7 @@
       </c>
       <c r="DJ2" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DK2" t="inlineStr">
@@ -1623,7 +1628,7 @@
       </c>
       <c r="DM2" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DN2" t="inlineStr">
@@ -1638,15 +1643,20 @@
       </c>
       <c r="DP2" t="inlineStr">
         <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="DQ2" t="inlineStr">
+        <is>
           <t>operations</t>
         </is>
       </c>
-      <c r="DQ2" t="inlineStr">
+      <c r="DR2" t="inlineStr">
         <is>
           <t>scheduling</t>
         </is>
       </c>
-      <c r="DR2" t="inlineStr">
+      <c r="DS2" t="inlineStr">
         <is>
           <t>job_maintenance_plan</t>
         </is>
@@ -1665,12 +1675,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1680,7 +1690,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1700,7 +1710,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1715,12 +1725,12 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1730,7 +1740,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -1760,7 +1770,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1790,12 +1800,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1815,12 +1825,12 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1850,17 +1860,17 @@
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
@@ -1875,7 +1885,7 @@
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
@@ -1885,12 +1895,12 @@
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
@@ -1915,12 +1925,12 @@
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
@@ -1955,12 +1965,12 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BK3" t="inlineStr">
@@ -1990,7 +2000,7 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -2000,27 +2010,27 @@
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -2030,7 +2040,7 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
@@ -2040,7 +2050,7 @@
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -2055,12 +2065,12 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
@@ -2075,12 +2085,12 @@
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
@@ -2090,12 +2100,12 @@
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
@@ -2130,42 +2140,42 @@
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CU3" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CV3" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CW3" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CX3" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CY3" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CZ3" t="inlineStr">
@@ -2180,12 +2190,12 @@
       </c>
       <c r="DB3" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DC3" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DD3" t="inlineStr">
@@ -2205,7 +2215,7 @@
       </c>
       <c r="DG3" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DH3" t="inlineStr">
@@ -2220,7 +2230,7 @@
       </c>
       <c r="DJ3" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DK3" t="inlineStr">
@@ -2230,12 +2240,12 @@
       </c>
       <c r="DL3" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DM3" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DN3" t="inlineStr">
@@ -2250,15 +2260,20 @@
       </c>
       <c r="DP3" t="inlineStr">
         <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="DQ3" t="inlineStr">
+        <is>
           <t>operations</t>
         </is>
       </c>
-      <c r="DQ3" t="inlineStr">
+      <c r="DR3" t="inlineStr">
         <is>
           <t>scheduling</t>
         </is>
       </c>
-      <c r="DR3" t="inlineStr">
+      <c r="DS3" t="inlineStr">
         <is>
           <t>job_staff_roster</t>
         </is>
@@ -2277,7 +2292,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -2287,17 +2302,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -2307,12 +2322,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -2337,22 +2352,22 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -2367,12 +2382,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -2382,12 +2397,12 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -2397,7 +2412,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -2422,12 +2437,12 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
@@ -2442,7 +2457,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -2472,12 +2487,12 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
@@ -2487,7 +2502,7 @@
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
@@ -2497,7 +2512,7 @@
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
@@ -2512,12 +2527,12 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
@@ -2567,12 +2582,12 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BK4" t="inlineStr">
@@ -2582,7 +2597,7 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
@@ -2592,7 +2607,7 @@
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
@@ -2607,12 +2622,12 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2627,12 +2642,12 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2707,7 +2722,7 @@
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
@@ -2722,17 +2737,17 @@
       </c>
       <c r="CN4" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CO4" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CP4" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CQ4" t="inlineStr">
@@ -2752,7 +2767,7 @@
       </c>
       <c r="CT4" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CU4" t="inlineStr">
@@ -2762,27 +2777,27 @@
       </c>
       <c r="CV4" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CW4" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CX4" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CY4" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CZ4" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DA4" t="inlineStr">
@@ -2792,12 +2807,12 @@
       </c>
       <c r="DB4" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DC4" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DD4" t="inlineStr">
@@ -2817,22 +2832,22 @@
       </c>
       <c r="DG4" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DH4" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DI4" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DJ4" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DK4" t="inlineStr">
@@ -2857,20 +2872,25 @@
       </c>
       <c r="DO4" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DP4" t="inlineStr">
         <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="DQ4" t="inlineStr">
+        <is>
           <t>operations</t>
         </is>
       </c>
-      <c r="DQ4" t="inlineStr">
+      <c r="DR4" t="inlineStr">
         <is>
           <t>scheduling</t>
         </is>
       </c>
-      <c r="DR4" t="inlineStr">
+      <c r="DS4" t="inlineStr">
         <is>
           <t>job_resource_alloc</t>
         </is>
@@ -2904,22 +2924,22 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -2944,12 +2964,12 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -2964,7 +2984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -2974,7 +2994,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -3029,7 +3049,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -3039,17 +3059,17 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -3059,22 +3079,22 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -3104,12 +3124,12 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
@@ -3134,12 +3154,12 @@
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
@@ -3159,12 +3179,12 @@
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
@@ -3179,12 +3199,12 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BK5" t="inlineStr">
@@ -3199,12 +3219,12 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
@@ -3214,12 +3234,12 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -3239,17 +3259,17 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BX5" t="inlineStr">
@@ -3259,7 +3279,7 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -3294,22 +3314,22 @@
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
@@ -3329,7 +3349,7 @@
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
@@ -3339,7 +3359,7 @@
       </c>
       <c r="CO5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CP5" t="inlineStr">
@@ -3354,12 +3374,12 @@
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
@@ -3379,22 +3399,22 @@
       </c>
       <c r="CW5" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CX5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CY5" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CZ5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DA5" t="inlineStr">
@@ -3404,7 +3424,7 @@
       </c>
       <c r="DB5" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DC5" t="inlineStr">
@@ -3414,7 +3434,7 @@
       </c>
       <c r="DD5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DE5" t="inlineStr">
@@ -3424,7 +3444,7 @@
       </c>
       <c r="DF5" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DG5" t="inlineStr">
@@ -3434,7 +3454,7 @@
       </c>
       <c r="DH5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DI5" t="inlineStr">
@@ -3444,7 +3464,7 @@
       </c>
       <c r="DJ5" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DK5" t="inlineStr">
@@ -3454,7 +3474,7 @@
       </c>
       <c r="DL5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DM5" t="inlineStr">
@@ -3474,15 +3494,20 @@
       </c>
       <c r="DP5" t="inlineStr">
         <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="DQ5" t="inlineStr">
+        <is>
           <t>operations</t>
         </is>
       </c>
-      <c r="DQ5" t="inlineStr">
+      <c r="DR5" t="inlineStr">
         <is>
           <t>logistics</t>
         </is>
       </c>
-      <c r="DR5" t="inlineStr">
+      <c r="DS5" t="inlineStr">
         <is>
           <t>job_warehouse_mgmt</t>
         </is>
@@ -3526,12 +3551,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -3556,17 +3581,17 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -3586,7 +3611,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -3606,12 +3631,12 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -3621,22 +3646,22 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
@@ -3651,7 +3676,7 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
@@ -3661,12 +3686,12 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -3681,7 +3706,7 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
@@ -3696,12 +3721,12 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
@@ -3731,12 +3756,12 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -3761,12 +3786,12 @@
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -3781,7 +3806,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -3791,7 +3816,7 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
@@ -3801,12 +3826,12 @@
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
@@ -3846,22 +3871,22 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BX6" t="inlineStr">
@@ -3891,12 +3916,12 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
@@ -3936,12 +3961,12 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
@@ -3976,12 +4001,12 @@
       </c>
       <c r="CT6" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CU6" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CV6" t="inlineStr">
@@ -4001,7 +4026,7 @@
       </c>
       <c r="CY6" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CZ6" t="inlineStr">
@@ -4011,7 +4036,7 @@
       </c>
       <c r="DA6" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DB6" t="inlineStr">
@@ -4046,7 +4071,7 @@
       </c>
       <c r="DH6" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DI6" t="inlineStr">
@@ -4066,7 +4091,7 @@
       </c>
       <c r="DL6" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DM6" t="inlineStr">
@@ -4076,25 +4101,30 @@
       </c>
       <c r="DN6" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DO6" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DP6" t="inlineStr">
         <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="DQ6" t="inlineStr">
+        <is>
           <t>operations</t>
         </is>
       </c>
-      <c r="DQ6" t="inlineStr">
+      <c r="DR6" t="inlineStr">
         <is>
           <t>logistics</t>
         </is>
       </c>
-      <c r="DR6" t="inlineStr">
+      <c r="DS6" t="inlineStr">
         <is>
           <t>job_shipment_track</t>
         </is>
@@ -4128,27 +4158,27 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -4168,17 +4198,17 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -4188,7 +4218,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -4198,7 +4228,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -4213,12 +4243,12 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -4238,7 +4268,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -4248,7 +4278,7 @@
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
@@ -4268,7 +4298,7 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
@@ -4278,7 +4308,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -4298,12 +4328,12 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
@@ -4323,7 +4353,7 @@
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
@@ -4333,7 +4363,7 @@
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
@@ -4353,12 +4383,12 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
@@ -4383,12 +4413,12 @@
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
@@ -4398,7 +4428,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -4408,7 +4438,7 @@
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BK7" t="inlineStr">
@@ -4448,7 +4478,7 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -4463,7 +4493,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -4493,12 +4523,12 @@
       </c>
       <c r="CA7" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CC7" t="inlineStr">
@@ -4508,7 +4538,7 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
@@ -4523,7 +4553,7 @@
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -4533,12 +4563,12 @@
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CK7" t="inlineStr">
@@ -4553,17 +4583,17 @@
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CO7" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CP7" t="inlineStr">
@@ -4583,7 +4613,7 @@
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
@@ -4593,12 +4623,12 @@
       </c>
       <c r="CU7" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CV7" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CW7" t="inlineStr">
@@ -4613,17 +4643,17 @@
       </c>
       <c r="CY7" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CZ7" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DA7" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DB7" t="inlineStr">
@@ -4633,7 +4663,7 @@
       </c>
       <c r="DC7" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DD7" t="inlineStr">
@@ -4673,12 +4703,12 @@
       </c>
       <c r="DK7" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DL7" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DM7" t="inlineStr">
@@ -4688,25 +4718,30 @@
       </c>
       <c r="DN7" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DO7" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DP7" t="inlineStr">
         <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="DQ7" t="inlineStr">
+        <is>
           <t>operations</t>
         </is>
       </c>
-      <c r="DQ7" t="inlineStr">
+      <c r="DR7" t="inlineStr">
         <is>
           <t>logistics</t>
         </is>
       </c>
-      <c r="DR7" t="inlineStr">
+      <c r="DS7" t="inlineStr">
         <is>
           <t>job_inventory_check</t>
         </is>
@@ -4730,17 +4765,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -4750,7 +4785,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -4770,7 +4805,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -4780,7 +4815,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -4800,17 +4835,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -4820,17 +4855,17 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -4840,12 +4875,12 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -4860,7 +4895,7 @@
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
@@ -4870,17 +4905,17 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
@@ -4900,7 +4935,7 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
@@ -4910,7 +4945,7 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -4925,22 +4960,22 @@
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -4955,7 +4990,7 @@
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
@@ -4970,7 +5005,7 @@
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -4980,12 +5015,12 @@
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
@@ -5015,22 +5050,22 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
@@ -5050,12 +5085,12 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -5065,12 +5100,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -5080,12 +5115,12 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BX8" t="inlineStr">
@@ -5095,22 +5130,22 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CC8" t="inlineStr">
@@ -5125,12 +5160,12 @@
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -5185,12 +5220,12 @@
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
@@ -5225,12 +5260,12 @@
       </c>
       <c r="CY8" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CZ8" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DA8" t="inlineStr">
@@ -5250,7 +5285,7 @@
       </c>
       <c r="DD8" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DE8" t="inlineStr">
@@ -5260,17 +5295,17 @@
       </c>
       <c r="DF8" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DG8" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DH8" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DI8" t="inlineStr">
@@ -5295,30 +5330,35 @@
       </c>
       <c r="DM8" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DN8" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DO8" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DP8" t="inlineStr">
         <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="DQ8" t="inlineStr">
+        <is>
           <t>hr</t>
         </is>
       </c>
-      <c r="DQ8" t="inlineStr">
+      <c r="DR8" t="inlineStr">
         <is>
           <t>payroll</t>
         </is>
       </c>
-      <c r="DR8" t="inlineStr">
+      <c r="DS8" t="inlineStr">
         <is>
           <t>job_tax_withhold</t>
         </is>
@@ -5332,7 +5372,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -5357,7 +5397,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -5367,17 +5407,17 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -5392,12 +5432,12 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -5407,7 +5447,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -5417,7 +5457,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -5437,7 +5477,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -5447,17 +5487,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -5492,7 +5532,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
@@ -5507,17 +5547,17 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
@@ -5532,12 +5572,12 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
@@ -5547,12 +5587,12 @@
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -5567,12 +5607,12 @@
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -5602,12 +5642,12 @@
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
@@ -5627,12 +5667,12 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BK9" t="inlineStr">
@@ -5642,7 +5682,7 @@
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
@@ -5652,7 +5692,7 @@
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
@@ -5702,7 +5742,7 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
@@ -5712,7 +5752,7 @@
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -5737,12 +5777,12 @@
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -5777,12 +5817,12 @@
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CO9" t="inlineStr">
@@ -5807,7 +5847,7 @@
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
@@ -5817,7 +5857,7 @@
       </c>
       <c r="CU9" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CV9" t="inlineStr">
@@ -5827,7 +5867,7 @@
       </c>
       <c r="CW9" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CX9" t="inlineStr">
@@ -5837,17 +5877,17 @@
       </c>
       <c r="CY9" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CZ9" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DA9" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DB9" t="inlineStr">
@@ -5857,12 +5897,12 @@
       </c>
       <c r="DC9" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DD9" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DE9" t="inlineStr">
@@ -5882,7 +5922,7 @@
       </c>
       <c r="DH9" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DI9" t="inlineStr">
@@ -5897,7 +5937,7 @@
       </c>
       <c r="DK9" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DL9" t="inlineStr">
@@ -5917,20 +5957,25 @@
       </c>
       <c r="DO9" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DP9" t="inlineStr">
         <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="DQ9" t="inlineStr">
+        <is>
           <t>hr</t>
         </is>
       </c>
-      <c r="DQ9" t="inlineStr">
+      <c r="DR9" t="inlineStr">
         <is>
           <t>payroll</t>
         </is>
       </c>
-      <c r="DR9" t="inlineStr">
+      <c r="DS9" t="inlineStr">
         <is>
           <t>job_salary_calc</t>
         </is>
@@ -5944,7 +5989,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -5954,7 +5999,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -5964,12 +6009,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -5979,7 +6024,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -5989,7 +6034,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -6004,12 +6049,12 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -6044,7 +6089,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -6054,7 +6099,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -6074,12 +6119,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
@@ -6089,12 +6134,12 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
@@ -6124,7 +6169,7 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -6144,7 +6189,7 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
@@ -6159,12 +6204,12 @@
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -6199,12 +6244,12 @@
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
@@ -6249,12 +6294,12 @@
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
@@ -6274,12 +6319,12 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -6289,7 +6334,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -6299,7 +6344,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -6319,7 +6364,7 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -6329,7 +6374,7 @@
       </c>
       <c r="CA10" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CB10" t="inlineStr">
@@ -6339,12 +6384,12 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -6359,12 +6404,12 @@
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
@@ -6379,12 +6424,12 @@
       </c>
       <c r="CK10" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
@@ -6409,22 +6454,22 @@
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CU10" t="inlineStr">
@@ -6449,7 +6494,7 @@
       </c>
       <c r="CY10" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CZ10" t="inlineStr">
@@ -6459,7 +6504,7 @@
       </c>
       <c r="DA10" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DB10" t="inlineStr">
@@ -6469,7 +6514,7 @@
       </c>
       <c r="DC10" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DD10" t="inlineStr">
@@ -6479,7 +6524,7 @@
       </c>
       <c r="DE10" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DF10" t="inlineStr">
@@ -6504,22 +6549,22 @@
       </c>
       <c r="DJ10" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DK10" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DL10" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DM10" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DN10" t="inlineStr">
@@ -6529,20 +6574,25 @@
       </c>
       <c r="DO10" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DP10" t="inlineStr">
         <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="DQ10" t="inlineStr">
+        <is>
           <t>hr</t>
         </is>
       </c>
-      <c r="DQ10" t="inlineStr">
+      <c r="DR10" t="inlineStr">
         <is>
           <t>payroll</t>
         </is>
       </c>
-      <c r="DR10" t="inlineStr">
+      <c r="DS10" t="inlineStr">
         <is>
           <t>job_bonus_process</t>
         </is>
@@ -6571,12 +6621,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6586,12 +6636,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -6601,12 +6651,12 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -6681,12 +6731,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -6711,12 +6761,12 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
@@ -6731,32 +6781,32 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
@@ -6791,7 +6841,7 @@
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
@@ -6801,7 +6851,7 @@
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
@@ -6811,12 +6861,12 @@
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
@@ -6846,12 +6896,12 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
@@ -6866,27 +6916,27 @@
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -6896,17 +6946,17 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -6926,7 +6976,7 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
@@ -6936,7 +6986,7 @@
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -6966,12 +7016,12 @@
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -7001,12 +7051,12 @@
       </c>
       <c r="CM11" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CN11" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CO11" t="inlineStr">
@@ -7031,7 +7081,7 @@
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
@@ -7041,7 +7091,7 @@
       </c>
       <c r="CU11" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CV11" t="inlineStr">
@@ -7051,12 +7101,12 @@
       </c>
       <c r="CW11" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CX11" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CY11" t="inlineStr">
@@ -7066,12 +7116,12 @@
       </c>
       <c r="CZ11" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DA11" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DB11" t="inlineStr">
@@ -7091,12 +7141,12 @@
       </c>
       <c r="DE11" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DF11" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DG11" t="inlineStr">
@@ -7106,22 +7156,22 @@
       </c>
       <c r="DH11" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DI11" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DJ11" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DK11" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DL11" t="inlineStr">
@@ -7146,15 +7196,20 @@
       </c>
       <c r="DP11" t="inlineStr">
         <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="DQ11" t="inlineStr">
+        <is>
           <t>hr</t>
         </is>
       </c>
-      <c r="DQ11" t="inlineStr">
+      <c r="DR11" t="inlineStr">
         <is>
           <t>recruiting</t>
         </is>
       </c>
-      <c r="DR11" t="inlineStr">
+      <c r="DS11" t="inlineStr">
         <is>
           <t>job_offer_gen</t>
         </is>
@@ -7178,7 +7233,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -7193,7 +7248,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -7203,12 +7258,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -7223,7 +7278,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -7233,7 +7288,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -7243,7 +7298,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -7253,7 +7308,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
@@ -7288,12 +7343,12 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -7318,7 +7373,7 @@
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
@@ -7333,7 +7388,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -7353,12 +7408,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -7373,32 +7428,32 @@
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
@@ -7418,12 +7473,12 @@
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
@@ -7433,7 +7488,7 @@
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
@@ -7443,17 +7498,17 @@
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -7463,7 +7518,7 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
@@ -7473,7 +7528,7 @@
       </c>
       <c r="BK12" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BL12" t="inlineStr">
@@ -7483,12 +7538,12 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
@@ -7503,7 +7558,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -7513,7 +7568,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -7528,27 +7583,27 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -7558,17 +7613,17 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
@@ -7578,7 +7633,7 @@
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -7593,7 +7648,7 @@
       </c>
       <c r="CI12" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CJ12" t="inlineStr">
@@ -7613,12 +7668,12 @@
       </c>
       <c r="CM12" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CN12" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CO12" t="inlineStr">
@@ -7628,12 +7683,12 @@
       </c>
       <c r="CP12" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
@@ -7653,12 +7708,12 @@
       </c>
       <c r="CU12" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CV12" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CW12" t="inlineStr">
@@ -7683,12 +7738,12 @@
       </c>
       <c r="DA12" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DB12" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DC12" t="inlineStr">
@@ -7713,17 +7768,17 @@
       </c>
       <c r="DG12" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DH12" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DI12" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DJ12" t="inlineStr">
@@ -7733,12 +7788,12 @@
       </c>
       <c r="DK12" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DL12" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DM12" t="inlineStr">
@@ -7748,7 +7803,7 @@
       </c>
       <c r="DN12" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DO12" t="inlineStr">
@@ -7758,15 +7813,20 @@
       </c>
       <c r="DP12" t="inlineStr">
         <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="DQ12" t="inlineStr">
+        <is>
           <t>hr</t>
         </is>
       </c>
-      <c r="DQ12" t="inlineStr">
+      <c r="DR12" t="inlineStr">
         <is>
           <t>recruiting</t>
         </is>
       </c>
-      <c r="DR12" t="inlineStr">
+      <c r="DS12" t="inlineStr">
         <is>
           <t>job_interview_sched</t>
         </is>
@@ -7790,12 +7850,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -7815,12 +7875,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -7845,7 +7905,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -7855,7 +7915,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -7865,12 +7925,12 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -7935,7 +7995,7 @@
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
@@ -7945,7 +8005,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -7955,12 +8015,12 @@
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -7985,22 +8045,22 @@
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -8030,17 +8090,17 @@
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
@@ -8050,7 +8110,7 @@
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -8070,7 +8130,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -8080,7 +8140,7 @@
       </c>
       <c r="BJ13" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BK13" t="inlineStr">
@@ -8090,12 +8150,12 @@
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
@@ -8115,12 +8175,12 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
@@ -8175,12 +8235,12 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
@@ -8190,7 +8250,7 @@
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -8200,7 +8260,7 @@
       </c>
       <c r="CH13" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CI13" t="inlineStr">
@@ -8220,22 +8280,22 @@
       </c>
       <c r="CL13" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CM13" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CN13" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CO13" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CP13" t="inlineStr">
@@ -8250,42 +8310,42 @@
       </c>
       <c r="CR13" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CS13" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CT13" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CU13" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CV13" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CW13" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CX13" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CY13" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CZ13" t="inlineStr">
@@ -8300,22 +8360,22 @@
       </c>
       <c r="DB13" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DC13" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DD13" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DE13" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DF13" t="inlineStr">
@@ -8350,7 +8410,7 @@
       </c>
       <c r="DL13" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DM13" t="inlineStr">
@@ -8370,15 +8430,20 @@
       </c>
       <c r="DP13" t="inlineStr">
         <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="DQ13" t="inlineStr">
+        <is>
           <t>hr</t>
         </is>
       </c>
-      <c r="DQ13" t="inlineStr">
+      <c r="DR13" t="inlineStr">
         <is>
           <t>recruiting</t>
         </is>
       </c>
-      <c r="DR13" t="inlineStr">
+      <c r="DS13" t="inlineStr">
         <is>
           <t>job_candidate_screen</t>
         </is>
@@ -8402,7 +8467,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -8412,7 +8477,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -8442,12 +8507,12 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -8512,12 +8577,12 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -8527,7 +8592,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
@@ -8557,7 +8622,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -8582,12 +8647,12 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
@@ -8612,22 +8677,22 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
@@ -8672,7 +8737,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BG14" t="inlineStr">
@@ -8687,7 +8752,7 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
@@ -8702,7 +8767,7 @@
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BM14" t="inlineStr">
@@ -8712,7 +8777,7 @@
       </c>
       <c r="BN14" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BO14" t="inlineStr">
@@ -8747,12 +8812,12 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -8767,12 +8832,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -8782,12 +8847,12 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
@@ -8797,7 +8862,7 @@
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
@@ -8812,7 +8877,7 @@
       </c>
       <c r="CH14" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CI14" t="inlineStr">
@@ -8862,12 +8927,12 @@
       </c>
       <c r="CR14" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CS14" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CT14" t="inlineStr">
@@ -8882,12 +8947,12 @@
       </c>
       <c r="CV14" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CW14" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CX14" t="inlineStr">
@@ -8917,12 +8982,12 @@
       </c>
       <c r="DC14" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DD14" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DE14" t="inlineStr">
@@ -8942,7 +9007,7 @@
       </c>
       <c r="DH14" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DI14" t="inlineStr">
@@ -8957,7 +9022,7 @@
       </c>
       <c r="DK14" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DL14" t="inlineStr">
@@ -8977,20 +9042,25 @@
       </c>
       <c r="DO14" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DP14" t="inlineStr">
         <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="DQ14" t="inlineStr">
+        <is>
           <t>marketing</t>
         </is>
       </c>
-      <c r="DQ14" t="inlineStr">
+      <c r="DR14" t="inlineStr">
         <is>
           <t>campaigns</t>
         </is>
       </c>
-      <c r="DR14" t="inlineStr">
+      <c r="DS14" t="inlineStr">
         <is>
           <t>job_segment_users</t>
         </is>
@@ -9004,27 +9074,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -9049,7 +9119,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -9059,7 +9129,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -9094,12 +9164,12 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -9124,12 +9194,12 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -9139,12 +9209,12 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
@@ -9169,12 +9239,12 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -9204,12 +9274,12 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
@@ -9219,12 +9289,12 @@
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -9244,7 +9314,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -9264,12 +9334,12 @@
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
@@ -9279,7 +9349,7 @@
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
@@ -9309,7 +9379,7 @@
       </c>
       <c r="BK15" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BL15" t="inlineStr">
@@ -9319,7 +9389,7 @@
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
@@ -9334,12 +9404,12 @@
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -9349,12 +9419,12 @@
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -9389,12 +9459,12 @@
       </c>
       <c r="CA15" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CC15" t="inlineStr">
@@ -9404,7 +9474,7 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
@@ -9414,27 +9484,27 @@
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CI15" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CJ15" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CK15" t="inlineStr">
@@ -9454,12 +9524,12 @@
       </c>
       <c r="CN15" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CO15" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CP15" t="inlineStr">
@@ -9484,17 +9554,17 @@
       </c>
       <c r="CT15" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CU15" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CV15" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CW15" t="inlineStr">
@@ -9514,7 +9584,7 @@
       </c>
       <c r="CZ15" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DA15" t="inlineStr">
@@ -9524,17 +9594,17 @@
       </c>
       <c r="DB15" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DC15" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DD15" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DE15" t="inlineStr">
@@ -9544,7 +9614,7 @@
       </c>
       <c r="DF15" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DG15" t="inlineStr">
@@ -9579,12 +9649,12 @@
       </c>
       <c r="DM15" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DN15" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DO15" t="inlineStr">
@@ -9594,15 +9664,20 @@
       </c>
       <c r="DP15" t="inlineStr">
         <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="DQ15" t="inlineStr">
+        <is>
           <t>marketing</t>
         </is>
       </c>
-      <c r="DQ15" t="inlineStr">
+      <c r="DR15" t="inlineStr">
         <is>
           <t>campaigns</t>
         </is>
       </c>
-      <c r="DR15" t="inlineStr">
+      <c r="DS15" t="inlineStr">
         <is>
           <t>job_update_crm</t>
         </is>
@@ -9616,17 +9691,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -9641,12 +9716,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -9656,7 +9731,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -9671,17 +9746,17 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -9696,32 +9771,32 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -9756,7 +9831,7 @@
       </c>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
@@ -9771,17 +9846,17 @@
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -9796,7 +9871,7 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -9806,12 +9881,12 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
@@ -9821,7 +9896,7 @@
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
@@ -9866,7 +9941,7 @@
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
@@ -9876,17 +9951,17 @@
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -9926,7 +10001,7 @@
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BM16" t="inlineStr">
@@ -9941,7 +10016,7 @@
       </c>
       <c r="BO16" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BP16" t="inlineStr">
@@ -9951,7 +10026,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -9966,7 +10041,7 @@
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -10011,12 +10086,12 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
@@ -10076,22 +10151,22 @@
       </c>
       <c r="CP16" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CQ16" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CR16" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CS16" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CT16" t="inlineStr">
@@ -10141,7 +10216,7 @@
       </c>
       <c r="DC16" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DD16" t="inlineStr">
@@ -10156,17 +10231,17 @@
       </c>
       <c r="DF16" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DG16" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DH16" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DI16" t="inlineStr">
@@ -10176,12 +10251,12 @@
       </c>
       <c r="DJ16" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DK16" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DL16" t="inlineStr">
@@ -10191,12 +10266,12 @@
       </c>
       <c r="DM16" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DN16" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DO16" t="inlineStr">
@@ -10206,15 +10281,20 @@
       </c>
       <c r="DP16" t="inlineStr">
         <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="DQ16" t="inlineStr">
+        <is>
           <t>marketing</t>
         </is>
       </c>
-      <c r="DQ16" t="inlineStr">
+      <c r="DR16" t="inlineStr">
         <is>
           <t>campaigns</t>
         </is>
       </c>
-      <c r="DR16" t="inlineStr">
+      <c r="DS16" t="inlineStr">
         <is>
           <t>job_email_blast</t>
         </is>
@@ -10233,7 +10313,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -10263,22 +10343,22 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -10293,12 +10373,12 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -10308,22 +10388,22 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -10338,12 +10418,12 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
@@ -10353,12 +10433,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -10368,22 +10448,22 @@
       </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
@@ -10398,32 +10478,32 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
@@ -10453,12 +10533,12 @@
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
@@ -10473,22 +10553,22 @@
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
@@ -10503,7 +10583,7 @@
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
@@ -10513,7 +10593,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -10553,12 +10633,12 @@
       </c>
       <c r="BO17" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
@@ -10573,12 +10653,12 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -10653,7 +10733,7 @@
       </c>
       <c r="CI17" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CJ17" t="inlineStr">
@@ -10663,12 +10743,12 @@
       </c>
       <c r="CK17" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CL17" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CM17" t="inlineStr">
@@ -10678,7 +10758,7 @@
       </c>
       <c r="CN17" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CO17" t="inlineStr">
@@ -10723,12 +10803,12 @@
       </c>
       <c r="CW17" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CX17" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CY17" t="inlineStr">
@@ -10743,12 +10823,12 @@
       </c>
       <c r="DA17" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DB17" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DC17" t="inlineStr">
@@ -10763,7 +10843,7 @@
       </c>
       <c r="DE17" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DF17" t="inlineStr">
@@ -10773,27 +10853,27 @@
       </c>
       <c r="DG17" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DH17" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DI17" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DJ17" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DK17" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DL17" t="inlineStr">
@@ -10813,20 +10893,25 @@
       </c>
       <c r="DO17" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DP17" t="inlineStr">
         <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="DQ17" t="inlineStr">
+        <is>
           <t>marketing</t>
         </is>
       </c>
-      <c r="DQ17" t="inlineStr">
+      <c r="DR17" t="inlineStr">
         <is>
           <t>analytics</t>
         </is>
       </c>
-      <c r="DR17" t="inlineStr">
+      <c r="DS17" t="inlineStr">
         <is>
           <t>job_web_traffic</t>
         </is>
@@ -10860,22 +10945,22 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -10895,12 +10980,12 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -10935,12 +11020,12 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
@@ -10950,7 +11035,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -10960,17 +11045,17 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -10985,12 +11070,12 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
@@ -11030,27 +11115,27 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -11060,17 +11145,17 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
@@ -11080,7 +11165,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -11090,7 +11175,7 @@
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
@@ -11100,7 +11185,7 @@
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
@@ -11110,7 +11195,7 @@
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -11125,32 +11210,32 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BK18" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BM18" t="inlineStr">
@@ -11180,12 +11265,12 @@
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -11200,12 +11285,12 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BX18" t="inlineStr">
@@ -11220,22 +11305,22 @@
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
@@ -11245,17 +11330,17 @@
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -11270,7 +11355,7 @@
       </c>
       <c r="CJ18" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CK18" t="inlineStr">
@@ -11345,12 +11430,12 @@
       </c>
       <c r="CY18" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CZ18" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DA18" t="inlineStr">
@@ -11375,22 +11460,22 @@
       </c>
       <c r="DE18" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DF18" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DG18" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DH18" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DI18" t="inlineStr">
@@ -11410,12 +11495,12 @@
       </c>
       <c r="DL18" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DM18" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DN18" t="inlineStr">
@@ -11430,15 +11515,20 @@
       </c>
       <c r="DP18" t="inlineStr">
         <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="DQ18" t="inlineStr">
+        <is>
           <t>marketing</t>
         </is>
       </c>
-      <c r="DQ18" t="inlineStr">
+      <c r="DR18" t="inlineStr">
         <is>
           <t>analytics</t>
         </is>
       </c>
-      <c r="DR18" t="inlineStr">
+      <c r="DS18" t="inlineStr">
         <is>
           <t>job_conversion_rate</t>
         </is>
@@ -11472,22 +11562,22 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -11522,7 +11612,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -11537,7 +11627,7 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
@@ -11562,7 +11652,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -11577,12 +11667,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -11592,7 +11682,7 @@
       </c>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
@@ -11607,12 +11697,12 @@
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
@@ -11627,12 +11717,12 @@
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
@@ -11652,12 +11742,12 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
@@ -11667,12 +11757,12 @@
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -11702,12 +11792,12 @@
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
@@ -11717,7 +11807,7 @@
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
@@ -11727,7 +11817,7 @@
       </c>
       <c r="BE19" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BF19" t="inlineStr">
@@ -11772,7 +11862,7 @@
       </c>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BO19" t="inlineStr">
@@ -11782,7 +11872,7 @@
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
@@ -11832,12 +11922,12 @@
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CB19" t="inlineStr">
@@ -11862,7 +11952,7 @@
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -11877,7 +11967,7 @@
       </c>
       <c r="CI19" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CJ19" t="inlineStr">
@@ -11917,12 +12007,12 @@
       </c>
       <c r="CQ19" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CR19" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CS19" t="inlineStr">
@@ -11932,7 +12022,7 @@
       </c>
       <c r="CT19" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CU19" t="inlineStr">
@@ -11942,17 +12032,17 @@
       </c>
       <c r="CV19" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CW19" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CX19" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CY19" t="inlineStr">
@@ -11972,7 +12062,7 @@
       </c>
       <c r="DB19" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DC19" t="inlineStr">
@@ -11987,17 +12077,17 @@
       </c>
       <c r="DE19" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DF19" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DG19" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DH19" t="inlineStr">
@@ -12007,7 +12097,7 @@
       </c>
       <c r="DI19" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DJ19" t="inlineStr">
@@ -12017,7 +12107,7 @@
       </c>
       <c r="DK19" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DL19" t="inlineStr">
@@ -12032,7 +12122,7 @@
       </c>
       <c r="DN19" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DO19" t="inlineStr">
@@ -12042,15 +12132,20 @@
       </c>
       <c r="DP19" t="inlineStr">
         <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="DQ19" t="inlineStr">
+        <is>
           <t>marketing</t>
         </is>
       </c>
-      <c r="DQ19" t="inlineStr">
+      <c r="DR19" t="inlineStr">
         <is>
           <t>analytics</t>
         </is>
       </c>
-      <c r="DR19" t="inlineStr">
+      <c r="DS19" t="inlineStr">
         <is>
           <t>job_roi_report</t>
         </is>
@@ -12064,7 +12159,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -12084,22 +12179,22 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -12109,17 +12204,17 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -12149,7 +12244,7 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
@@ -12159,32 +12254,32 @@
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -12209,7 +12304,7 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -12219,7 +12314,7 @@
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
@@ -12234,7 +12329,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
@@ -12249,7 +12344,7 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
@@ -12269,17 +12364,17 @@
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr">
@@ -12289,17 +12384,17 @@
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
@@ -12309,7 +12404,7 @@
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
@@ -12319,7 +12414,7 @@
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
@@ -12349,32 +12444,32 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BJ20" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BK20" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BM20" t="inlineStr">
@@ -12394,12 +12489,12 @@
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -12409,17 +12504,17 @@
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -12429,7 +12524,7 @@
       </c>
       <c r="BW20" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BX20" t="inlineStr">
@@ -12444,12 +12539,12 @@
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CB20" t="inlineStr">
@@ -12474,7 +12569,7 @@
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -12489,7 +12584,7 @@
       </c>
       <c r="CI20" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CJ20" t="inlineStr">
@@ -12504,12 +12599,12 @@
       </c>
       <c r="CL20" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CM20" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CN20" t="inlineStr">
@@ -12519,7 +12614,7 @@
       </c>
       <c r="CO20" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CP20" t="inlineStr">
@@ -12529,7 +12624,7 @@
       </c>
       <c r="CQ20" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CR20" t="inlineStr">
@@ -12589,12 +12684,12 @@
       </c>
       <c r="DC20" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DD20" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DE20" t="inlineStr">
@@ -12649,20 +12744,25 @@
       </c>
       <c r="DO20" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DP20" t="inlineStr">
         <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="DQ20" t="inlineStr">
+        <is>
           <t>finance</t>
         </is>
       </c>
-      <c r="DQ20" t="inlineStr">
+      <c r="DR20" t="inlineStr">
         <is>
           <t>reporting</t>
         </is>
       </c>
-      <c r="DR20" t="inlineStr">
+      <c r="DS20" t="inlineStr">
         <is>
           <t>job_report_daily</t>
         </is>
@@ -12681,7 +12781,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -12691,17 +12791,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -12736,7 +12836,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -12746,7 +12846,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -12786,12 +12886,12 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
@@ -12811,7 +12911,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
@@ -12821,7 +12921,7 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -12846,7 +12946,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -12856,7 +12956,7 @@
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
@@ -12871,12 +12971,12 @@
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
@@ -12891,7 +12991,7 @@
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
@@ -12906,7 +13006,7 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
@@ -12916,12 +13016,12 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
@@ -12931,12 +13031,12 @@
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
@@ -12961,22 +13061,22 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BK21" t="inlineStr">
@@ -13006,7 +13106,7 @@
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
@@ -13021,17 +13121,17 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -13041,12 +13141,12 @@
       </c>
       <c r="BW21" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
@@ -13061,17 +13161,17 @@
       </c>
       <c r="CA21" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
@@ -13081,7 +13181,7 @@
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
@@ -13091,12 +13191,12 @@
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CI21" t="inlineStr">
@@ -13141,7 +13241,7 @@
       </c>
       <c r="CQ21" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CR21" t="inlineStr">
@@ -13156,7 +13256,7 @@
       </c>
       <c r="CT21" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CU21" t="inlineStr">
@@ -13171,12 +13271,12 @@
       </c>
       <c r="CW21" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CX21" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CY21" t="inlineStr">
@@ -13191,7 +13291,7 @@
       </c>
       <c r="DA21" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DB21" t="inlineStr">
@@ -13201,7 +13301,7 @@
       </c>
       <c r="DC21" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DD21" t="inlineStr">
@@ -13211,32 +13311,32 @@
       </c>
       <c r="DE21" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DF21" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DG21" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DH21" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DI21" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DJ21" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DK21" t="inlineStr">
@@ -13266,15 +13366,20 @@
       </c>
       <c r="DP21" t="inlineStr">
         <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="DQ21" t="inlineStr">
+        <is>
           <t>finance</t>
         </is>
       </c>
-      <c r="DQ21" t="inlineStr">
+      <c r="DR21" t="inlineStr">
         <is>
           <t>reporting</t>
         </is>
       </c>
-      <c r="DR21" t="inlineStr">
+      <c r="DS21" t="inlineStr">
         <is>
           <t>job_report_weekly</t>
         </is>
@@ -13298,12 +13403,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -13313,12 +13418,12 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -13353,12 +13458,12 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -13378,12 +13483,12 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -13393,12 +13498,12 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -13413,7 +13518,7 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -13438,7 +13543,7 @@
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
@@ -13463,7 +13568,7 @@
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
@@ -13473,7 +13578,7 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
@@ -13508,12 +13613,12 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AV22" t="inlineStr">
@@ -13533,12 +13638,12 @@
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
@@ -13563,22 +13668,22 @@
       </c>
       <c r="BE22" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -13603,12 +13708,12 @@
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BO22" t="inlineStr">
@@ -13633,7 +13738,7 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -13643,7 +13748,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -13668,12 +13773,12 @@
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CB22" t="inlineStr">
@@ -13683,7 +13788,7 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
@@ -13693,12 +13798,12 @@
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -13708,7 +13813,7 @@
       </c>
       <c r="CH22" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CI22" t="inlineStr">
@@ -13728,12 +13833,12 @@
       </c>
       <c r="CL22" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CM22" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CN22" t="inlineStr">
@@ -13763,12 +13868,12 @@
       </c>
       <c r="CS22" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CT22" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CU22" t="inlineStr">
@@ -13823,7 +13928,7 @@
       </c>
       <c r="DE22" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DF22" t="inlineStr">
@@ -13833,7 +13938,7 @@
       </c>
       <c r="DG22" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DH22" t="inlineStr">
@@ -13853,12 +13958,12 @@
       </c>
       <c r="DK22" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DL22" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DM22" t="inlineStr">
@@ -13868,25 +13973,30 @@
       </c>
       <c r="DN22" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DO22" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DP22" t="inlineStr">
         <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="DQ22" t="inlineStr">
+        <is>
           <t>finance</t>
         </is>
       </c>
-      <c r="DQ22" t="inlineStr">
+      <c r="DR22" t="inlineStr">
         <is>
           <t>reporting</t>
         </is>
       </c>
-      <c r="DR22" t="inlineStr">
+      <c r="DS22" t="inlineStr">
         <is>
           <t>job_report_monthly</t>
         </is>
@@ -13900,7 +14010,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -13910,12 +14020,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -13930,12 +14040,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -13945,12 +14055,12 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -13960,7 +14070,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -13970,7 +14080,7 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -13990,7 +14100,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -14000,27 +14110,27 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -14055,7 +14165,7 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
@@ -14065,7 +14175,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
@@ -14090,22 +14200,22 @@
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
@@ -14145,12 +14255,12 @@
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
@@ -14165,12 +14275,12 @@
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -14185,12 +14295,12 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -14215,7 +14325,7 @@
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
@@ -14225,7 +14335,7 @@
       </c>
       <c r="BO23" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BP23" t="inlineStr">
@@ -14250,12 +14360,12 @@
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -14265,7 +14375,7 @@
       </c>
       <c r="BW23" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BX23" t="inlineStr">
@@ -14275,7 +14385,7 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -14310,12 +14420,12 @@
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">
@@ -14325,12 +14435,12 @@
       </c>
       <c r="CI23" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CJ23" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CK23" t="inlineStr">
@@ -14380,7 +14490,7 @@
       </c>
       <c r="CT23" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CU23" t="inlineStr">
@@ -14390,12 +14500,12 @@
       </c>
       <c r="CV23" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CW23" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CX23" t="inlineStr">
@@ -14415,7 +14525,7 @@
       </c>
       <c r="DA23" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DB23" t="inlineStr">
@@ -14425,7 +14535,7 @@
       </c>
       <c r="DC23" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DD23" t="inlineStr">
@@ -14435,27 +14545,27 @@
       </c>
       <c r="DE23" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DF23" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DG23" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DH23" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DI23" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DJ23" t="inlineStr">
@@ -14465,22 +14575,22 @@
       </c>
       <c r="DK23" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DL23" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DM23" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DN23" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DO23" t="inlineStr">
@@ -14490,15 +14600,20 @@
       </c>
       <c r="DP23" t="inlineStr">
         <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="DQ23" t="inlineStr">
+        <is>
           <t>finance</t>
         </is>
       </c>
-      <c r="DQ23" t="inlineStr">
+      <c r="DR23" t="inlineStr">
         <is>
           <t>billing</t>
         </is>
       </c>
-      <c r="DR23" t="inlineStr">
+      <c r="DS23" t="inlineStr">
         <is>
           <t>job_payment_proc</t>
         </is>
@@ -14527,12 +14642,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -14542,12 +14657,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -14557,12 +14672,12 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -14622,12 +14737,12 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
@@ -14637,12 +14752,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -14672,12 +14787,12 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
@@ -14707,17 +14822,17 @@
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
@@ -14727,7 +14842,7 @@
       </c>
       <c r="AS24" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr">
@@ -14752,7 +14867,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -14767,17 +14882,17 @@
       </c>
       <c r="BA24" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BD24" t="inlineStr">
@@ -14797,7 +14912,7 @@
       </c>
       <c r="BG24" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BH24" t="inlineStr">
@@ -14812,7 +14927,7 @@
       </c>
       <c r="BJ24" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BK24" t="inlineStr">
@@ -14827,12 +14942,12 @@
       </c>
       <c r="BM24" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BN24" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BO24" t="inlineStr">
@@ -14857,12 +14972,12 @@
       </c>
       <c r="BS24" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BT24" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BU24" t="inlineStr">
@@ -14962,22 +15077,22 @@
       </c>
       <c r="CN24" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CO24" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CP24" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CQ24" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CR24" t="inlineStr">
@@ -14992,12 +15107,12 @@
       </c>
       <c r="CT24" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CU24" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CV24" t="inlineStr">
@@ -15022,22 +15137,22 @@
       </c>
       <c r="CZ24" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DA24" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DB24" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DC24" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DD24" t="inlineStr">
@@ -15052,22 +15167,22 @@
       </c>
       <c r="DF24" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DG24" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DH24" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DI24" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DJ24" t="inlineStr">
@@ -15077,22 +15192,22 @@
       </c>
       <c r="DK24" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DL24" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DM24" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DN24" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DO24" t="inlineStr">
@@ -15102,15 +15217,20 @@
       </c>
       <c r="DP24" t="inlineStr">
         <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="DQ24" t="inlineStr">
+        <is>
           <t>finance</t>
         </is>
       </c>
-      <c r="DQ24" t="inlineStr">
+      <c r="DR24" t="inlineStr">
         <is>
           <t>billing</t>
         </is>
       </c>
-      <c r="DR24" t="inlineStr">
+      <c r="DS24" t="inlineStr">
         <is>
           <t>job_tax_calc</t>
         </is>
@@ -15139,17 +15259,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -15214,12 +15334,12 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
@@ -15239,12 +15359,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -15254,7 +15374,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -15264,7 +15384,7 @@
       </c>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AE25" t="inlineStr">
@@ -15294,12 +15414,12 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AL25" t="inlineStr">
@@ -15364,12 +15484,12 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AZ25" t="inlineStr">
@@ -15384,17 +15504,17 @@
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BD25" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BE25" t="inlineStr">
@@ -15404,7 +15524,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BG25" t="inlineStr">
@@ -15429,7 +15549,7 @@
       </c>
       <c r="BK25" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BL25" t="inlineStr">
@@ -15439,7 +15559,7 @@
       </c>
       <c r="BM25" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BN25" t="inlineStr">
@@ -15464,22 +15584,22 @@
       </c>
       <c r="BR25" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BS25" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BT25" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BU25" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BV25" t="inlineStr">
@@ -15509,12 +15629,12 @@
       </c>
       <c r="CA25" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CC25" t="inlineStr">
@@ -15524,12 +15644,12 @@
       </c>
       <c r="CD25" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CE25" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CF25" t="inlineStr">
@@ -15554,17 +15674,17 @@
       </c>
       <c r="CJ25" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CK25" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CL25" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CM25" t="inlineStr">
@@ -15574,7 +15694,7 @@
       </c>
       <c r="CN25" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CO25" t="inlineStr">
@@ -15599,12 +15719,12 @@
       </c>
       <c r="CS25" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CT25" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CU25" t="inlineStr">
@@ -15614,52 +15734,52 @@
       </c>
       <c r="CV25" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CW25" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CX25" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CY25" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CZ25" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DA25" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DB25" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DC25" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DD25" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DE25" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DF25" t="inlineStr">
@@ -15669,12 +15789,12 @@
       </c>
       <c r="DG25" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DH25" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DI25" t="inlineStr">
@@ -15689,7 +15809,7 @@
       </c>
       <c r="DK25" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DL25" t="inlineStr">
@@ -15699,7 +15819,7 @@
       </c>
       <c r="DM25" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DN25" t="inlineStr">
@@ -15714,15 +15834,20 @@
       </c>
       <c r="DP25" t="inlineStr">
         <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="DQ25" t="inlineStr">
+        <is>
           <t>finance</t>
         </is>
       </c>
-      <c r="DQ25" t="inlineStr">
+      <c r="DR25" t="inlineStr">
         <is>
           <t>billing</t>
         </is>
       </c>
-      <c r="DR25" t="inlineStr">
+      <c r="DS25" t="inlineStr">
         <is>
           <t>job_invoice_gen</t>
         </is>

--- a/data/log_analysis_tracker.xlsx
+++ b/data/log_analysis_tracker.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DS25"/>
+  <dimension ref="A1:DT25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,610 +436,615 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>analysis_results_20260205</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>analysis_results_20260203</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20260201</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20260129</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20260127</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20260125</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20260122</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20260120</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20260118</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20260115</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20260113</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20260111</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20260108</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20260106</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20260104</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20260101</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20251230</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20251228</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20251225</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20251223</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20251221</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20251218</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20251216</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20251214</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20251211</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20251209</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20251207</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20251204</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20251202</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20251130</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20251127</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20251125</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20251123</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20251120</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20251118</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20251116</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20251113</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20251111</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20251109</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20251106</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20251104</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20251102</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20251030</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20251028</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20251026</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20251023</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20251021</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20251019</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20251016</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20251014</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20251012</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20251009</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20251007</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20251005</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20251002</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250930</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250928</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250925</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250923</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250921</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250918</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250916</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250914</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250911</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250909</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250907</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250904</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250902</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250831</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250828</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250826</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250824</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250821</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250819</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250817</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250814</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250812</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250810</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250807</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250805</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250803</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250731</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250729</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250727</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250724</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250722</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250720</t>
         </is>
       </c>
-      <c r="CJ1" s="1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250717</t>
         </is>
       </c>
-      <c r="CK1" s="1" t="inlineStr">
+      <c r="CL1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250715</t>
         </is>
       </c>
-      <c r="CL1" s="1" t="inlineStr">
+      <c r="CM1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250713</t>
         </is>
       </c>
-      <c r="CM1" s="1" t="inlineStr">
+      <c r="CN1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250710</t>
         </is>
       </c>
-      <c r="CN1" s="1" t="inlineStr">
+      <c r="CO1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250708</t>
         </is>
       </c>
-      <c r="CO1" s="1" t="inlineStr">
+      <c r="CP1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250706</t>
         </is>
       </c>
-      <c r="CP1" s="1" t="inlineStr">
+      <c r="CQ1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250703</t>
         </is>
       </c>
-      <c r="CQ1" s="1" t="inlineStr">
+      <c r="CR1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250701</t>
         </is>
       </c>
-      <c r="CR1" s="1" t="inlineStr">
+      <c r="CS1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250629</t>
         </is>
       </c>
-      <c r="CS1" s="1" t="inlineStr">
+      <c r="CT1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250626</t>
         </is>
       </c>
-      <c r="CT1" s="1" t="inlineStr">
+      <c r="CU1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250624</t>
         </is>
       </c>
-      <c r="CU1" s="1" t="inlineStr">
+      <c r="CV1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250622</t>
         </is>
       </c>
-      <c r="CV1" s="1" t="inlineStr">
+      <c r="CW1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250619</t>
         </is>
       </c>
-      <c r="CW1" s="1" t="inlineStr">
+      <c r="CX1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250617</t>
         </is>
       </c>
-      <c r="CX1" s="1" t="inlineStr">
+      <c r="CY1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250615</t>
         </is>
       </c>
-      <c r="CY1" s="1" t="inlineStr">
+      <c r="CZ1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250612</t>
         </is>
       </c>
-      <c r="CZ1" s="1" t="inlineStr">
+      <c r="DA1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250610</t>
         </is>
       </c>
-      <c r="DA1" s="1" t="inlineStr">
+      <c r="DB1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250608</t>
         </is>
       </c>
-      <c r="DB1" s="1" t="inlineStr">
+      <c r="DC1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250605</t>
         </is>
       </c>
-      <c r="DC1" s="1" t="inlineStr">
+      <c r="DD1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250603</t>
         </is>
       </c>
-      <c r="DD1" s="1" t="inlineStr">
+      <c r="DE1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250601</t>
         </is>
       </c>
-      <c r="DE1" s="1" t="inlineStr">
+      <c r="DF1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250529</t>
         </is>
       </c>
-      <c r="DF1" s="1" t="inlineStr">
+      <c r="DG1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250527</t>
         </is>
       </c>
-      <c r="DG1" s="1" t="inlineStr">
+      <c r="DH1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250525</t>
         </is>
       </c>
-      <c r="DH1" s="1" t="inlineStr">
+      <c r="DI1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250522</t>
         </is>
       </c>
-      <c r="DI1" s="1" t="inlineStr">
+      <c r="DJ1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250520</t>
         </is>
       </c>
-      <c r="DJ1" s="1" t="inlineStr">
+      <c r="DK1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250518</t>
         </is>
       </c>
-      <c r="DK1" s="1" t="inlineStr">
+      <c r="DL1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250515</t>
         </is>
       </c>
-      <c r="DL1" s="1" t="inlineStr">
+      <c r="DM1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250513</t>
         </is>
       </c>
-      <c r="DM1" s="1" t="inlineStr">
+      <c r="DN1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250511</t>
         </is>
       </c>
-      <c r="DN1" s="1" t="inlineStr">
+      <c r="DO1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250508</t>
         </is>
       </c>
-      <c r="DO1" s="1" t="inlineStr">
+      <c r="DP1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250506</t>
         </is>
       </c>
-      <c r="DP1" s="1" t="inlineStr">
+      <c r="DQ1" s="1" t="inlineStr">
         <is>
           <t>analysis_results_20250505</t>
         </is>
       </c>
-      <c r="DQ1" s="1" t="inlineStr">
+      <c r="DR1" s="1" t="inlineStr">
         <is>
           <t>project</t>
         </is>
       </c>
-      <c r="DR1" s="1" t="inlineStr">
+      <c r="DS1" s="1" t="inlineStr">
         <is>
           <t>department</t>
         </is>
       </c>
-      <c r="DS1" s="1" t="inlineStr">
+      <c r="DT1" s="1" t="inlineStr">
         <is>
           <t>job_name</t>
         </is>
@@ -1053,12 +1058,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1093,12 +1098,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -1108,7 +1113,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -1118,7 +1123,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -1133,12 +1138,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -1208,12 +1213,12 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -1233,12 +1238,12 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
@@ -1248,17 +1253,17 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
@@ -1268,17 +1273,17 @@
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
@@ -1303,12 +1308,12 @@
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
@@ -1343,12 +1348,12 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
@@ -1368,7 +1373,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1378,17 +1383,17 @@
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1413,7 +1418,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1423,12 +1428,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1438,27 +1443,27 @@
       </c>
       <c r="CA2" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
@@ -1468,12 +1473,12 @@
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
@@ -1488,12 +1493,12 @@
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
@@ -1508,12 +1513,12 @@
       </c>
       <c r="CO2" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CP2" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CQ2" t="inlineStr">
@@ -1578,27 +1583,27 @@
       </c>
       <c r="DC2" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DD2" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DE2" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DF2" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DG2" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DH2" t="inlineStr">
@@ -1618,7 +1623,7 @@
       </c>
       <c r="DK2" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DL2" t="inlineStr">
@@ -1633,7 +1638,7 @@
       </c>
       <c r="DN2" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DO2" t="inlineStr">
@@ -1648,15 +1653,20 @@
       </c>
       <c r="DQ2" t="inlineStr">
         <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="DR2" t="inlineStr">
+        <is>
           <t>operations</t>
         </is>
       </c>
-      <c r="DR2" t="inlineStr">
+      <c r="DS2" t="inlineStr">
         <is>
           <t>scheduling</t>
         </is>
       </c>
-      <c r="DS2" t="inlineStr">
+      <c r="DT2" t="inlineStr">
         <is>
           <t>job_maintenance_plan</t>
         </is>
@@ -1670,7 +1680,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1680,12 +1690,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1695,7 +1705,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1715,7 +1725,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1730,12 +1740,12 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -1745,7 +1755,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -1775,7 +1785,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1805,12 +1815,12 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -1830,12 +1840,12 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -1865,17 +1875,17 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
@@ -1890,7 +1900,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1900,12 +1910,12 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
@@ -1930,12 +1940,12 @@
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
@@ -1970,12 +1980,12 @@
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BL3" t="inlineStr">
@@ -2005,7 +2015,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -2015,27 +2025,27 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BX3" t="inlineStr">
@@ -2045,7 +2055,7 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -2055,7 +2065,7 @@
       </c>
       <c r="CA3" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CB3" t="inlineStr">
@@ -2070,12 +2080,12 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
@@ -2090,12 +2100,12 @@
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
@@ -2105,12 +2115,12 @@
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
@@ -2145,42 +2155,42 @@
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CU3" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CV3" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CW3" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CX3" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CY3" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CZ3" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DA3" t="inlineStr">
@@ -2195,12 +2205,12 @@
       </c>
       <c r="DC3" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DD3" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DE3" t="inlineStr">
@@ -2220,7 +2230,7 @@
       </c>
       <c r="DH3" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DI3" t="inlineStr">
@@ -2235,7 +2245,7 @@
       </c>
       <c r="DK3" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DL3" t="inlineStr">
@@ -2245,12 +2255,12 @@
       </c>
       <c r="DM3" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DN3" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DO3" t="inlineStr">
@@ -2265,15 +2275,20 @@
       </c>
       <c r="DQ3" t="inlineStr">
         <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="DR3" t="inlineStr">
+        <is>
           <t>operations</t>
         </is>
       </c>
-      <c r="DR3" t="inlineStr">
+      <c r="DS3" t="inlineStr">
         <is>
           <t>scheduling</t>
         </is>
       </c>
-      <c r="DS3" t="inlineStr">
+      <c r="DT3" t="inlineStr">
         <is>
           <t>job_staff_roster</t>
         </is>
@@ -2297,7 +2312,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -2307,17 +2322,17 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -2327,12 +2342,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -2357,22 +2372,22 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -2387,12 +2402,12 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -2402,12 +2417,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -2417,7 +2432,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2442,12 +2457,12 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
@@ -2462,7 +2477,7 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -2492,12 +2507,12 @@
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -2507,7 +2522,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -2517,7 +2532,7 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
@@ -2532,12 +2547,12 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
@@ -2587,12 +2602,12 @@
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BL4" t="inlineStr">
@@ -2602,7 +2617,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2612,7 +2627,7 @@
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
@@ -2627,12 +2642,12 @@
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2647,12 +2662,12 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BX4" t="inlineStr">
@@ -2727,7 +2742,7 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
@@ -2742,17 +2757,17 @@
       </c>
       <c r="CO4" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CP4" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
@@ -2772,7 +2787,7 @@
       </c>
       <c r="CU4" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CV4" t="inlineStr">
@@ -2782,27 +2797,27 @@
       </c>
       <c r="CW4" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CX4" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CY4" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CZ4" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DA4" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DB4" t="inlineStr">
@@ -2812,12 +2827,12 @@
       </c>
       <c r="DC4" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DD4" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DE4" t="inlineStr">
@@ -2837,22 +2852,22 @@
       </c>
       <c r="DH4" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DI4" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DJ4" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DK4" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DL4" t="inlineStr">
@@ -2877,20 +2892,25 @@
       </c>
       <c r="DP4" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DQ4" t="inlineStr">
         <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="DR4" t="inlineStr">
+        <is>
           <t>operations</t>
         </is>
       </c>
-      <c r="DR4" t="inlineStr">
+      <c r="DS4" t="inlineStr">
         <is>
           <t>scheduling</t>
         </is>
       </c>
-      <c r="DS4" t="inlineStr">
+      <c r="DT4" t="inlineStr">
         <is>
           <t>job_resource_alloc</t>
         </is>
@@ -2904,7 +2924,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2929,22 +2949,22 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2969,12 +2989,12 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -2989,7 +3009,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -2999,7 +3019,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -3054,7 +3074,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
@@ -3064,17 +3084,17 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -3084,22 +3104,22 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
@@ -3129,12 +3149,12 @@
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
@@ -3159,12 +3179,12 @@
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
@@ -3184,12 +3204,12 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -3204,12 +3224,12 @@
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BL5" t="inlineStr">
@@ -3224,12 +3244,12 @@
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
@@ -3239,12 +3259,12 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -3264,17 +3284,17 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
@@ -3284,7 +3304,7 @@
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -3319,22 +3339,22 @@
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CK5" t="inlineStr">
@@ -3354,7 +3374,7 @@
       </c>
       <c r="CN5" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CO5" t="inlineStr">
@@ -3364,7 +3384,7 @@
       </c>
       <c r="CP5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CQ5" t="inlineStr">
@@ -3379,12 +3399,12 @@
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CU5" t="inlineStr">
@@ -3404,22 +3424,22 @@
       </c>
       <c r="CX5" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CY5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CZ5" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DA5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DB5" t="inlineStr">
@@ -3429,7 +3449,7 @@
       </c>
       <c r="DC5" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DD5" t="inlineStr">
@@ -3439,7 +3459,7 @@
       </c>
       <c r="DE5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DF5" t="inlineStr">
@@ -3449,7 +3469,7 @@
       </c>
       <c r="DG5" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DH5" t="inlineStr">
@@ -3459,7 +3479,7 @@
       </c>
       <c r="DI5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DJ5" t="inlineStr">
@@ -3469,7 +3489,7 @@
       </c>
       <c r="DK5" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DL5" t="inlineStr">
@@ -3479,7 +3499,7 @@
       </c>
       <c r="DM5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DN5" t="inlineStr">
@@ -3499,15 +3519,20 @@
       </c>
       <c r="DQ5" t="inlineStr">
         <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="DR5" t="inlineStr">
+        <is>
           <t>operations</t>
         </is>
       </c>
-      <c r="DR5" t="inlineStr">
+      <c r="DS5" t="inlineStr">
         <is>
           <t>logistics</t>
         </is>
       </c>
-      <c r="DS5" t="inlineStr">
+      <c r="DT5" t="inlineStr">
         <is>
           <t>job_warehouse_mgmt</t>
         </is>
@@ -3556,12 +3581,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -3586,17 +3611,17 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -3616,7 +3641,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -3636,12 +3661,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -3651,22 +3676,22 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -3681,7 +3706,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
@@ -3691,12 +3716,12 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -3711,7 +3736,7 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -3726,12 +3751,12 @@
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -3761,12 +3786,12 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
@@ -3791,12 +3816,12 @@
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
@@ -3811,7 +3836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -3821,7 +3846,7 @@
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BK6" t="inlineStr">
@@ -3831,12 +3856,12 @@
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -3876,22 +3901,22 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
@@ -3921,12 +3946,12 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
@@ -3966,12 +3991,12 @@
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CO6" t="inlineStr">
@@ -4006,12 +4031,12 @@
       </c>
       <c r="CU6" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CV6" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CW6" t="inlineStr">
@@ -4031,7 +4056,7 @@
       </c>
       <c r="CZ6" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DA6" t="inlineStr">
@@ -4041,7 +4066,7 @@
       </c>
       <c r="DB6" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DC6" t="inlineStr">
@@ -4076,7 +4101,7 @@
       </c>
       <c r="DI6" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DJ6" t="inlineStr">
@@ -4096,7 +4121,7 @@
       </c>
       <c r="DM6" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DN6" t="inlineStr">
@@ -4106,25 +4131,30 @@
       </c>
       <c r="DO6" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DP6" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DQ6" t="inlineStr">
         <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="DR6" t="inlineStr">
+        <is>
           <t>operations</t>
         </is>
       </c>
-      <c r="DR6" t="inlineStr">
+      <c r="DS6" t="inlineStr">
         <is>
           <t>logistics</t>
         </is>
       </c>
-      <c r="DS6" t="inlineStr">
+      <c r="DT6" t="inlineStr">
         <is>
           <t>job_shipment_track</t>
         </is>
@@ -4138,7 +4168,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -4163,27 +4193,27 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -4203,17 +4233,17 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -4223,7 +4253,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -4233,7 +4263,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -4248,12 +4278,12 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -4273,7 +4303,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
@@ -4283,7 +4313,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -4303,7 +4333,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -4313,7 +4343,7 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -4333,12 +4363,12 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
@@ -4358,7 +4388,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -4368,7 +4398,7 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
@@ -4388,12 +4418,12 @@
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
@@ -4418,12 +4448,12 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -4433,7 +4463,7 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
@@ -4443,7 +4473,7 @@
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BL7" t="inlineStr">
@@ -4483,7 +4513,7 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -4498,7 +4528,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -4528,12 +4558,12 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
@@ -4543,7 +4573,7 @@
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
@@ -4558,7 +4588,7 @@
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
@@ -4568,12 +4598,12 @@
       </c>
       <c r="CJ7" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CK7" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CL7" t="inlineStr">
@@ -4588,17 +4618,17 @@
       </c>
       <c r="CN7" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CO7" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CP7" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CQ7" t="inlineStr">
@@ -4618,7 +4648,7 @@
       </c>
       <c r="CT7" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CU7" t="inlineStr">
@@ -4628,12 +4658,12 @@
       </c>
       <c r="CV7" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CW7" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CX7" t="inlineStr">
@@ -4648,17 +4678,17 @@
       </c>
       <c r="CZ7" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DA7" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DB7" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DC7" t="inlineStr">
@@ -4668,7 +4698,7 @@
       </c>
       <c r="DD7" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DE7" t="inlineStr">
@@ -4708,12 +4738,12 @@
       </c>
       <c r="DL7" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DM7" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DN7" t="inlineStr">
@@ -4723,25 +4753,30 @@
       </c>
       <c r="DO7" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DP7" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DQ7" t="inlineStr">
         <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="DR7" t="inlineStr">
+        <is>
           <t>operations</t>
         </is>
       </c>
-      <c r="DR7" t="inlineStr">
+      <c r="DS7" t="inlineStr">
         <is>
           <t>logistics</t>
         </is>
       </c>
-      <c r="DS7" t="inlineStr">
+      <c r="DT7" t="inlineStr">
         <is>
           <t>job_inventory_check</t>
         </is>
@@ -4770,17 +4805,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -4790,7 +4825,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -4810,7 +4845,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -4820,7 +4855,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -4840,17 +4875,17 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -4860,17 +4895,17 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -4880,12 +4915,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4900,7 +4935,7 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -4910,17 +4945,17 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -4940,7 +4975,7 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
@@ -4950,7 +4985,7 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
@@ -4965,22 +5000,22 @@
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
@@ -4995,7 +5030,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -5010,7 +5045,7 @@
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
@@ -5020,12 +5055,12 @@
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -5055,22 +5090,22 @@
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -5090,12 +5125,12 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -5105,12 +5140,12 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -5120,12 +5155,12 @@
       </c>
       <c r="BW8" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
@@ -5135,22 +5170,22 @@
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
@@ -5165,12 +5200,12 @@
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -5225,12 +5260,12 @@
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
@@ -5265,12 +5300,12 @@
       </c>
       <c r="CZ8" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DA8" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DB8" t="inlineStr">
@@ -5290,7 +5325,7 @@
       </c>
       <c r="DE8" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DF8" t="inlineStr">
@@ -5300,17 +5335,17 @@
       </c>
       <c r="DG8" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DH8" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DI8" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DJ8" t="inlineStr">
@@ -5335,30 +5370,35 @@
       </c>
       <c r="DN8" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DO8" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DP8" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DQ8" t="inlineStr">
         <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="DR8" t="inlineStr">
+        <is>
           <t>hr</t>
         </is>
       </c>
-      <c r="DR8" t="inlineStr">
+      <c r="DS8" t="inlineStr">
         <is>
           <t>payroll</t>
         </is>
       </c>
-      <c r="DS8" t="inlineStr">
+      <c r="DT8" t="inlineStr">
         <is>
           <t>job_tax_withhold</t>
         </is>
@@ -5372,12 +5412,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -5402,7 +5442,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -5412,17 +5452,17 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -5437,12 +5477,12 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -5452,7 +5492,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -5462,7 +5502,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -5482,7 +5522,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -5492,17 +5532,17 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -5537,7 +5577,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -5552,17 +5592,17 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -5577,12 +5617,12 @@
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -5592,12 +5632,12 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
@@ -5612,12 +5652,12 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
@@ -5647,12 +5687,12 @@
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
@@ -5672,12 +5712,12 @@
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BL9" t="inlineStr">
@@ -5687,7 +5727,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -5697,7 +5737,7 @@
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
@@ -5747,7 +5787,7 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -5757,7 +5797,7 @@
       </c>
       <c r="CA9" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CB9" t="inlineStr">
@@ -5782,12 +5822,12 @@
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -5822,12 +5862,12 @@
       </c>
       <c r="CN9" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CO9" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CP9" t="inlineStr">
@@ -5852,7 +5892,7 @@
       </c>
       <c r="CT9" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CU9" t="inlineStr">
@@ -5862,7 +5902,7 @@
       </c>
       <c r="CV9" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CW9" t="inlineStr">
@@ -5872,7 +5912,7 @@
       </c>
       <c r="CX9" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CY9" t="inlineStr">
@@ -5882,17 +5922,17 @@
       </c>
       <c r="CZ9" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DA9" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DB9" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DC9" t="inlineStr">
@@ -5902,12 +5942,12 @@
       </c>
       <c r="DD9" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DE9" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DF9" t="inlineStr">
@@ -5927,7 +5967,7 @@
       </c>
       <c r="DI9" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DJ9" t="inlineStr">
@@ -5942,7 +5982,7 @@
       </c>
       <c r="DL9" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DM9" t="inlineStr">
@@ -5962,20 +6002,25 @@
       </c>
       <c r="DP9" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DQ9" t="inlineStr">
         <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="DR9" t="inlineStr">
+        <is>
           <t>hr</t>
         </is>
       </c>
-      <c r="DR9" t="inlineStr">
+      <c r="DS9" t="inlineStr">
         <is>
           <t>payroll</t>
         </is>
       </c>
-      <c r="DS9" t="inlineStr">
+      <c r="DT9" t="inlineStr">
         <is>
           <t>job_salary_calc</t>
         </is>
@@ -5989,12 +6034,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -6004,7 +6049,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -6014,12 +6059,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -6029,7 +6074,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -6039,7 +6084,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -6054,12 +6099,12 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -6094,7 +6139,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -6104,7 +6149,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -6124,12 +6169,12 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
@@ -6139,12 +6184,12 @@
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
@@ -6174,7 +6219,7 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
@@ -6194,7 +6239,7 @@
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
@@ -6209,12 +6254,12 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
@@ -6249,12 +6294,12 @@
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
@@ -6299,12 +6344,12 @@
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -6324,12 +6369,12 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
@@ -6339,7 +6384,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -6349,7 +6394,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -6369,7 +6414,7 @@
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -6379,7 +6424,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CC10" t="inlineStr">
@@ -6389,12 +6434,12 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
@@ -6409,12 +6454,12 @@
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CJ10" t="inlineStr">
@@ -6429,12 +6474,12 @@
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
@@ -6459,22 +6504,22 @@
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CU10" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CV10" t="inlineStr">
@@ -6499,7 +6544,7 @@
       </c>
       <c r="CZ10" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DA10" t="inlineStr">
@@ -6509,7 +6554,7 @@
       </c>
       <c r="DB10" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DC10" t="inlineStr">
@@ -6519,7 +6564,7 @@
       </c>
       <c r="DD10" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DE10" t="inlineStr">
@@ -6529,7 +6574,7 @@
       </c>
       <c r="DF10" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DG10" t="inlineStr">
@@ -6554,22 +6599,22 @@
       </c>
       <c r="DK10" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DL10" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DM10" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DN10" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DO10" t="inlineStr">
@@ -6579,20 +6624,25 @@
       </c>
       <c r="DP10" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DQ10" t="inlineStr">
         <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="DR10" t="inlineStr">
+        <is>
           <t>hr</t>
         </is>
       </c>
-      <c r="DR10" t="inlineStr">
+      <c r="DS10" t="inlineStr">
         <is>
           <t>payroll</t>
         </is>
       </c>
-      <c r="DS10" t="inlineStr">
+      <c r="DT10" t="inlineStr">
         <is>
           <t>job_bonus_process</t>
         </is>
@@ -6606,7 +6656,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -6626,12 +6676,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -6641,12 +6691,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -6656,12 +6706,12 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -6736,12 +6786,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
@@ -6766,12 +6816,12 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -6786,32 +6836,32 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
@@ -6846,7 +6896,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -6856,7 +6906,7 @@
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
@@ -6866,12 +6916,12 @@
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
@@ -6901,12 +6951,12 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BK11" t="inlineStr">
@@ -6921,27 +6971,27 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -6951,17 +7001,17 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -6981,7 +7031,7 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -6991,7 +7041,7 @@
       </c>
       <c r="CA11" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CB11" t="inlineStr">
@@ -7021,12 +7071,12 @@
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CI11" t="inlineStr">
@@ -7056,12 +7106,12 @@
       </c>
       <c r="CN11" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CO11" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CP11" t="inlineStr">
@@ -7086,7 +7136,7 @@
       </c>
       <c r="CT11" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CU11" t="inlineStr">
@@ -7096,7 +7146,7 @@
       </c>
       <c r="CV11" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CW11" t="inlineStr">
@@ -7106,12 +7156,12 @@
       </c>
       <c r="CX11" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CY11" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CZ11" t="inlineStr">
@@ -7121,12 +7171,12 @@
       </c>
       <c r="DA11" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DB11" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DC11" t="inlineStr">
@@ -7146,12 +7196,12 @@
       </c>
       <c r="DF11" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DG11" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DH11" t="inlineStr">
@@ -7161,22 +7211,22 @@
       </c>
       <c r="DI11" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DJ11" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DK11" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DL11" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DM11" t="inlineStr">
@@ -7201,15 +7251,20 @@
       </c>
       <c r="DQ11" t="inlineStr">
         <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="DR11" t="inlineStr">
+        <is>
           <t>hr</t>
         </is>
       </c>
-      <c r="DR11" t="inlineStr">
+      <c r="DS11" t="inlineStr">
         <is>
           <t>recruiting</t>
         </is>
       </c>
-      <c r="DS11" t="inlineStr">
+      <c r="DT11" t="inlineStr">
         <is>
           <t>job_offer_gen</t>
         </is>
@@ -7238,7 +7293,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -7253,7 +7308,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -7263,12 +7318,12 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -7283,7 +7338,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -7293,7 +7348,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -7303,7 +7358,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -7313,7 +7368,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -7348,12 +7403,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -7378,7 +7433,7 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
@@ -7393,7 +7448,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -7413,12 +7468,12 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
@@ -7433,32 +7488,32 @@
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
@@ -7478,12 +7533,12 @@
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
@@ -7493,7 +7548,7 @@
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -7503,17 +7558,17 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -7523,7 +7578,7 @@
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BK12" t="inlineStr">
@@ -7533,7 +7588,7 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
@@ -7543,12 +7598,12 @@
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
@@ -7563,7 +7618,7 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
@@ -7573,7 +7628,7 @@
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -7588,27 +7643,27 @@
       </c>
       <c r="BW12" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CB12" t="inlineStr">
@@ -7618,17 +7673,17 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
@@ -7638,7 +7693,7 @@
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -7653,7 +7708,7 @@
       </c>
       <c r="CJ12" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CK12" t="inlineStr">
@@ -7673,12 +7728,12 @@
       </c>
       <c r="CN12" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CO12" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CP12" t="inlineStr">
@@ -7688,12 +7743,12 @@
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">
@@ -7713,12 +7768,12 @@
       </c>
       <c r="CV12" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CW12" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CX12" t="inlineStr">
@@ -7743,12 +7798,12 @@
       </c>
       <c r="DB12" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DC12" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DD12" t="inlineStr">
@@ -7773,17 +7828,17 @@
       </c>
       <c r="DH12" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DI12" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DJ12" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DK12" t="inlineStr">
@@ -7793,12 +7848,12 @@
       </c>
       <c r="DL12" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DM12" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DN12" t="inlineStr">
@@ -7808,7 +7863,7 @@
       </c>
       <c r="DO12" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DP12" t="inlineStr">
@@ -7818,15 +7873,20 @@
       </c>
       <c r="DQ12" t="inlineStr">
         <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="DR12" t="inlineStr">
+        <is>
           <t>hr</t>
         </is>
       </c>
-      <c r="DR12" t="inlineStr">
+      <c r="DS12" t="inlineStr">
         <is>
           <t>recruiting</t>
         </is>
       </c>
-      <c r="DS12" t="inlineStr">
+      <c r="DT12" t="inlineStr">
         <is>
           <t>job_interview_sched</t>
         </is>
@@ -7840,7 +7900,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -7855,12 +7915,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -7880,12 +7940,12 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -7910,7 +7970,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -7920,7 +7980,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -7930,12 +7990,12 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -8000,7 +8060,7 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
@@ -8010,7 +8070,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -8020,12 +8080,12 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
@@ -8050,22 +8110,22 @@
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
@@ -8095,17 +8155,17 @@
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
@@ -8115,7 +8175,7 @@
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
@@ -8135,7 +8195,7 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
@@ -8145,7 +8205,7 @@
       </c>
       <c r="BK13" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BL13" t="inlineStr">
@@ -8155,12 +8215,12 @@
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BO13" t="inlineStr">
@@ -8180,12 +8240,12 @@
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -8240,12 +8300,12 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
@@ -8255,7 +8315,7 @@
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -8265,7 +8325,7 @@
       </c>
       <c r="CI13" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CJ13" t="inlineStr">
@@ -8285,22 +8345,22 @@
       </c>
       <c r="CM13" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CN13" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CO13" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CP13" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CQ13" t="inlineStr">
@@ -8315,42 +8375,42 @@
       </c>
       <c r="CS13" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CT13" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CU13" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CV13" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CW13" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CX13" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CY13" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CZ13" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DA13" t="inlineStr">
@@ -8365,22 +8425,22 @@
       </c>
       <c r="DC13" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DD13" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DE13" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DF13" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DG13" t="inlineStr">
@@ -8415,7 +8475,7 @@
       </c>
       <c r="DM13" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DN13" t="inlineStr">
@@ -8435,15 +8495,20 @@
       </c>
       <c r="DQ13" t="inlineStr">
         <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="DR13" t="inlineStr">
+        <is>
           <t>hr</t>
         </is>
       </c>
-      <c r="DR13" t="inlineStr">
+      <c r="DS13" t="inlineStr">
         <is>
           <t>recruiting</t>
         </is>
       </c>
-      <c r="DS13" t="inlineStr">
+      <c r="DT13" t="inlineStr">
         <is>
           <t>job_candidate_screen</t>
         </is>
@@ -8457,7 +8522,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -8472,7 +8537,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -8482,7 +8547,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -8512,12 +8577,12 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -8582,12 +8647,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -8597,7 +8662,7 @@
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
@@ -8627,7 +8692,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
@@ -8652,12 +8717,12 @@
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
@@ -8682,22 +8747,22 @@
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -8742,7 +8807,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -8757,7 +8822,7 @@
       </c>
       <c r="BJ14" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BK14" t="inlineStr">
@@ -8772,7 +8837,7 @@
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
@@ -8782,7 +8847,7 @@
       </c>
       <c r="BO14" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BP14" t="inlineStr">
@@ -8817,12 +8882,12 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BX14" t="inlineStr">
@@ -8837,12 +8902,12 @@
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CB14" t="inlineStr">
@@ -8852,12 +8917,12 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
@@ -8867,7 +8932,7 @@
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -8882,7 +8947,7 @@
       </c>
       <c r="CI14" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CJ14" t="inlineStr">
@@ -8932,12 +8997,12 @@
       </c>
       <c r="CS14" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CT14" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CU14" t="inlineStr">
@@ -8952,12 +9017,12 @@
       </c>
       <c r="CW14" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CX14" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CY14" t="inlineStr">
@@ -8987,12 +9052,12 @@
       </c>
       <c r="DD14" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DE14" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DF14" t="inlineStr">
@@ -9012,7 +9077,7 @@
       </c>
       <c r="DI14" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DJ14" t="inlineStr">
@@ -9027,7 +9092,7 @@
       </c>
       <c r="DL14" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DM14" t="inlineStr">
@@ -9047,20 +9112,25 @@
       </c>
       <c r="DP14" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DQ14" t="inlineStr">
         <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="DR14" t="inlineStr">
+        <is>
           <t>marketing</t>
         </is>
       </c>
-      <c r="DR14" t="inlineStr">
+      <c r="DS14" t="inlineStr">
         <is>
           <t>campaigns</t>
         </is>
       </c>
-      <c r="DS14" t="inlineStr">
+      <c r="DT14" t="inlineStr">
         <is>
           <t>job_segment_users</t>
         </is>
@@ -9074,32 +9144,32 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -9124,7 +9194,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -9134,7 +9204,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -9169,12 +9239,12 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -9199,12 +9269,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -9214,12 +9284,12 @@
       </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -9244,12 +9314,12 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
@@ -9279,12 +9349,12 @@
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -9294,12 +9364,12 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
@@ -9319,7 +9389,7 @@
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
@@ -9339,12 +9409,12 @@
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -9354,7 +9424,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BG15" t="inlineStr">
@@ -9384,7 +9454,7 @@
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BM15" t="inlineStr">
@@ -9394,7 +9464,7 @@
       </c>
       <c r="BN15" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BO15" t="inlineStr">
@@ -9409,12 +9479,12 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
@@ -9424,12 +9494,12 @@
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -9464,12 +9534,12 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
@@ -9479,7 +9549,7 @@
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
@@ -9489,27 +9559,27 @@
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CI15" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CJ15" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CK15" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CL15" t="inlineStr">
@@ -9529,12 +9599,12 @@
       </c>
       <c r="CO15" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CP15" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CQ15" t="inlineStr">
@@ -9559,17 +9629,17 @@
       </c>
       <c r="CU15" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CV15" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CW15" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CX15" t="inlineStr">
@@ -9589,7 +9659,7 @@
       </c>
       <c r="DA15" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DB15" t="inlineStr">
@@ -9599,17 +9669,17 @@
       </c>
       <c r="DC15" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DD15" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DE15" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DF15" t="inlineStr">
@@ -9619,7 +9689,7 @@
       </c>
       <c r="DG15" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DH15" t="inlineStr">
@@ -9654,12 +9724,12 @@
       </c>
       <c r="DN15" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DO15" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DP15" t="inlineStr">
@@ -9669,15 +9739,20 @@
       </c>
       <c r="DQ15" t="inlineStr">
         <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="DR15" t="inlineStr">
+        <is>
           <t>marketing</t>
         </is>
       </c>
-      <c r="DR15" t="inlineStr">
+      <c r="DS15" t="inlineStr">
         <is>
           <t>campaigns</t>
         </is>
       </c>
-      <c r="DS15" t="inlineStr">
+      <c r="DT15" t="inlineStr">
         <is>
           <t>job_update_crm</t>
         </is>
@@ -9691,22 +9766,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -9721,12 +9796,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -9736,7 +9811,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -9751,17 +9826,17 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -9776,32 +9851,32 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -9836,7 +9911,7 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -9851,17 +9926,17 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
@@ -9876,7 +9951,7 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
@@ -9886,12 +9961,12 @@
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
@@ -9901,7 +9976,7 @@
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -9946,7 +10021,7 @@
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
@@ -9956,17 +10031,17 @@
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
@@ -10006,7 +10081,7 @@
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
@@ -10021,7 +10096,7 @@
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
@@ -10031,7 +10106,7 @@
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
@@ -10046,7 +10121,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -10091,12 +10166,12 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
@@ -10156,22 +10231,22 @@
       </c>
       <c r="CQ16" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CR16" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CS16" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CT16" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CU16" t="inlineStr">
@@ -10221,7 +10296,7 @@
       </c>
       <c r="DD16" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DE16" t="inlineStr">
@@ -10236,17 +10311,17 @@
       </c>
       <c r="DG16" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DH16" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DI16" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DJ16" t="inlineStr">
@@ -10256,12 +10331,12 @@
       </c>
       <c r="DK16" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DL16" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DM16" t="inlineStr">
@@ -10271,12 +10346,12 @@
       </c>
       <c r="DN16" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DO16" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DP16" t="inlineStr">
@@ -10286,15 +10361,20 @@
       </c>
       <c r="DQ16" t="inlineStr">
         <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="DR16" t="inlineStr">
+        <is>
           <t>marketing</t>
         </is>
       </c>
-      <c r="DR16" t="inlineStr">
+      <c r="DS16" t="inlineStr">
         <is>
           <t>campaigns</t>
         </is>
       </c>
-      <c r="DS16" t="inlineStr">
+      <c r="DT16" t="inlineStr">
         <is>
           <t>job_email_blast</t>
         </is>
@@ -10308,7 +10388,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -10318,7 +10398,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -10348,22 +10428,22 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -10378,12 +10458,12 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -10393,22 +10473,22 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
@@ -10423,12 +10503,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -10438,12 +10518,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
@@ -10453,22 +10533,22 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
@@ -10483,32 +10563,32 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
@@ -10538,12 +10618,12 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
@@ -10558,22 +10638,22 @@
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
@@ -10588,7 +10668,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BG17" t="inlineStr">
@@ -10598,7 +10678,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -10638,12 +10718,12 @@
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -10658,12 +10738,12 @@
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -10738,7 +10818,7 @@
       </c>
       <c r="CJ17" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CK17" t="inlineStr">
@@ -10748,12 +10828,12 @@
       </c>
       <c r="CL17" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CM17" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CN17" t="inlineStr">
@@ -10763,7 +10843,7 @@
       </c>
       <c r="CO17" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CP17" t="inlineStr">
@@ -10808,12 +10888,12 @@
       </c>
       <c r="CX17" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CY17" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CZ17" t="inlineStr">
@@ -10828,12 +10908,12 @@
       </c>
       <c r="DB17" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DC17" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DD17" t="inlineStr">
@@ -10848,7 +10928,7 @@
       </c>
       <c r="DF17" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DG17" t="inlineStr">
@@ -10858,27 +10938,27 @@
       </c>
       <c r="DH17" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DI17" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DJ17" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DK17" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DL17" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DM17" t="inlineStr">
@@ -10898,20 +10978,25 @@
       </c>
       <c r="DP17" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DQ17" t="inlineStr">
         <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="DR17" t="inlineStr">
+        <is>
           <t>marketing</t>
         </is>
       </c>
-      <c r="DR17" t="inlineStr">
+      <c r="DS17" t="inlineStr">
         <is>
           <t>analytics</t>
         </is>
       </c>
-      <c r="DS17" t="inlineStr">
+      <c r="DT17" t="inlineStr">
         <is>
           <t>job_web_traffic</t>
         </is>
@@ -10950,22 +11035,22 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -10985,12 +11070,12 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -11025,12 +11110,12 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -11040,7 +11125,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
@@ -11050,17 +11135,17 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
@@ -11075,12 +11160,12 @@
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
@@ -11120,27 +11205,27 @@
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
@@ -11150,17 +11235,17 @@
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
@@ -11170,7 +11255,7 @@
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
@@ -11180,7 +11265,7 @@
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
@@ -11190,7 +11275,7 @@
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
@@ -11200,7 +11285,7 @@
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
@@ -11215,32 +11300,32 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BK18" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
@@ -11270,12 +11355,12 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -11290,12 +11375,12 @@
       </c>
       <c r="BW18" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
@@ -11310,22 +11395,22 @@
       </c>
       <c r="CA18" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
@@ -11335,17 +11420,17 @@
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CI18" t="inlineStr">
@@ -11360,7 +11445,7 @@
       </c>
       <c r="CK18" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CL18" t="inlineStr">
@@ -11435,12 +11520,12 @@
       </c>
       <c r="CZ18" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DA18" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DB18" t="inlineStr">
@@ -11465,22 +11550,22 @@
       </c>
       <c r="DF18" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DG18" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DH18" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DI18" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DJ18" t="inlineStr">
@@ -11500,12 +11585,12 @@
       </c>
       <c r="DM18" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DN18" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DO18" t="inlineStr">
@@ -11520,15 +11605,20 @@
       </c>
       <c r="DQ18" t="inlineStr">
         <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="DR18" t="inlineStr">
+        <is>
           <t>marketing</t>
         </is>
       </c>
-      <c r="DR18" t="inlineStr">
+      <c r="DS18" t="inlineStr">
         <is>
           <t>analytics</t>
         </is>
       </c>
-      <c r="DS18" t="inlineStr">
+      <c r="DT18" t="inlineStr">
         <is>
           <t>job_conversion_rate</t>
         </is>
@@ -11567,22 +11657,22 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -11617,7 +11707,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -11632,7 +11722,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -11657,7 +11747,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
@@ -11672,12 +11762,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
@@ -11687,7 +11777,7 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -11702,12 +11792,12 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -11722,12 +11812,12 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
@@ -11747,12 +11837,12 @@
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -11762,12 +11852,12 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
@@ -11797,12 +11887,12 @@
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
@@ -11812,7 +11902,7 @@
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -11822,7 +11912,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BG19" t="inlineStr">
@@ -11867,7 +11957,7 @@
       </c>
       <c r="BO19" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BP19" t="inlineStr">
@@ -11877,7 +11967,7 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -11927,12 +12017,12 @@
       </c>
       <c r="CA19" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CC19" t="inlineStr">
@@ -11957,7 +12047,7 @@
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -11972,7 +12062,7 @@
       </c>
       <c r="CJ19" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CK19" t="inlineStr">
@@ -12012,12 +12102,12 @@
       </c>
       <c r="CR19" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CS19" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CT19" t="inlineStr">
@@ -12027,7 +12117,7 @@
       </c>
       <c r="CU19" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CV19" t="inlineStr">
@@ -12037,17 +12127,17 @@
       </c>
       <c r="CW19" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CX19" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CY19" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CZ19" t="inlineStr">
@@ -12067,7 +12157,7 @@
       </c>
       <c r="DC19" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DD19" t="inlineStr">
@@ -12082,17 +12172,17 @@
       </c>
       <c r="DF19" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DG19" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DH19" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DI19" t="inlineStr">
@@ -12102,7 +12192,7 @@
       </c>
       <c r="DJ19" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DK19" t="inlineStr">
@@ -12112,7 +12202,7 @@
       </c>
       <c r="DL19" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DM19" t="inlineStr">
@@ -12127,7 +12217,7 @@
       </c>
       <c r="DO19" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DP19" t="inlineStr">
@@ -12137,15 +12227,20 @@
       </c>
       <c r="DQ19" t="inlineStr">
         <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="DR19" t="inlineStr">
+        <is>
           <t>marketing</t>
         </is>
       </c>
-      <c r="DR19" t="inlineStr">
+      <c r="DS19" t="inlineStr">
         <is>
           <t>analytics</t>
         </is>
       </c>
-      <c r="DS19" t="inlineStr">
+      <c r="DT19" t="inlineStr">
         <is>
           <t>job_roi_report</t>
         </is>
@@ -12159,12 +12254,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -12184,22 +12279,22 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -12209,17 +12304,17 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -12249,7 +12344,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -12259,32 +12354,32 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -12309,7 +12404,7 @@
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
@@ -12319,7 +12414,7 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
@@ -12334,7 +12429,7 @@
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
@@ -12349,7 +12444,7 @@
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -12369,17 +12464,17 @@
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -12389,17 +12484,17 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -12409,7 +12504,7 @@
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
@@ -12419,7 +12514,7 @@
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
@@ -12449,32 +12544,32 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BJ20" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BK20" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
@@ -12494,12 +12589,12 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
@@ -12509,17 +12604,17 @@
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -12529,7 +12624,7 @@
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
@@ -12544,12 +12639,12 @@
       </c>
       <c r="CA20" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CC20" t="inlineStr">
@@ -12574,7 +12669,7 @@
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -12589,7 +12684,7 @@
       </c>
       <c r="CJ20" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CK20" t="inlineStr">
@@ -12604,12 +12699,12 @@
       </c>
       <c r="CM20" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CN20" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CO20" t="inlineStr">
@@ -12619,7 +12714,7 @@
       </c>
       <c r="CP20" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CQ20" t="inlineStr">
@@ -12629,7 +12724,7 @@
       </c>
       <c r="CR20" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CS20" t="inlineStr">
@@ -12689,12 +12784,12 @@
       </c>
       <c r="DD20" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DE20" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DF20" t="inlineStr">
@@ -12749,20 +12844,25 @@
       </c>
       <c r="DP20" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DQ20" t="inlineStr">
         <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="DR20" t="inlineStr">
+        <is>
           <t>finance</t>
         </is>
       </c>
-      <c r="DR20" t="inlineStr">
+      <c r="DS20" t="inlineStr">
         <is>
           <t>reporting</t>
         </is>
       </c>
-      <c r="DS20" t="inlineStr">
+      <c r="DT20" t="inlineStr">
         <is>
           <t>job_report_daily</t>
         </is>
@@ -12786,7 +12886,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -12796,17 +12896,17 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -12841,7 +12941,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -12851,7 +12951,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -12891,12 +12991,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -12916,7 +13016,7 @@
       </c>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
@@ -12926,7 +13026,7 @@
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
@@ -12951,7 +13051,7 @@
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
@@ -12961,7 +13061,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
@@ -12976,12 +13076,12 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
@@ -12996,7 +13096,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -13011,7 +13111,7 @@
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
@@ -13021,12 +13121,12 @@
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
@@ -13036,12 +13136,12 @@
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
@@ -13066,22 +13166,22 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BK21" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BL21" t="inlineStr">
@@ -13111,7 +13211,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -13126,17 +13226,17 @@
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -13146,12 +13246,12 @@
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -13166,17 +13266,17 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
@@ -13186,7 +13286,7 @@
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -13196,12 +13296,12 @@
       </c>
       <c r="CH21" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CI21" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CJ21" t="inlineStr">
@@ -13246,7 +13346,7 @@
       </c>
       <c r="CR21" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CS21" t="inlineStr">
@@ -13261,7 +13361,7 @@
       </c>
       <c r="CU21" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CV21" t="inlineStr">
@@ -13276,12 +13376,12 @@
       </c>
       <c r="CX21" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CY21" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CZ21" t="inlineStr">
@@ -13296,7 +13396,7 @@
       </c>
       <c r="DB21" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DC21" t="inlineStr">
@@ -13306,7 +13406,7 @@
       </c>
       <c r="DD21" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DE21" t="inlineStr">
@@ -13316,32 +13416,32 @@
       </c>
       <c r="DF21" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DG21" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DH21" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DI21" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DJ21" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DK21" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DL21" t="inlineStr">
@@ -13371,15 +13471,20 @@
       </c>
       <c r="DQ21" t="inlineStr">
         <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="DR21" t="inlineStr">
+        <is>
           <t>finance</t>
         </is>
       </c>
-      <c r="DR21" t="inlineStr">
+      <c r="DS21" t="inlineStr">
         <is>
           <t>reporting</t>
         </is>
       </c>
-      <c r="DS21" t="inlineStr">
+      <c r="DT21" t="inlineStr">
         <is>
           <t>job_report_weekly</t>
         </is>
@@ -13408,12 +13513,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -13423,12 +13528,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -13463,12 +13568,12 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -13488,12 +13593,12 @@
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
@@ -13503,12 +13608,12 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
@@ -13523,7 +13628,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -13548,7 +13653,7 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
@@ -13573,7 +13678,7 @@
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
@@ -13583,7 +13688,7 @@
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
@@ -13618,12 +13723,12 @@
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
@@ -13643,12 +13748,12 @@
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
@@ -13673,22 +13778,22 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BJ22" t="inlineStr">
@@ -13713,12 +13818,12 @@
       </c>
       <c r="BN22" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BO22" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BP22" t="inlineStr">
@@ -13743,7 +13848,7 @@
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -13753,7 +13858,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -13778,12 +13883,12 @@
       </c>
       <c r="CA22" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CC22" t="inlineStr">
@@ -13793,7 +13898,7 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
@@ -13803,12 +13908,12 @@
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -13818,7 +13923,7 @@
       </c>
       <c r="CI22" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CJ22" t="inlineStr">
@@ -13838,12 +13943,12 @@
       </c>
       <c r="CM22" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CN22" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CO22" t="inlineStr">
@@ -13873,12 +13978,12 @@
       </c>
       <c r="CT22" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CU22" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CV22" t="inlineStr">
@@ -13933,7 +14038,7 @@
       </c>
       <c r="DF22" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DG22" t="inlineStr">
@@ -13943,7 +14048,7 @@
       </c>
       <c r="DH22" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DI22" t="inlineStr">
@@ -13963,12 +14068,12 @@
       </c>
       <c r="DL22" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DM22" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DN22" t="inlineStr">
@@ -13978,25 +14083,30 @@
       </c>
       <c r="DO22" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DP22" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DQ22" t="inlineStr">
         <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="DR22" t="inlineStr">
+        <is>
           <t>finance</t>
         </is>
       </c>
-      <c r="DR22" t="inlineStr">
+      <c r="DS22" t="inlineStr">
         <is>
           <t>reporting</t>
         </is>
       </c>
-      <c r="DS22" t="inlineStr">
+      <c r="DT22" t="inlineStr">
         <is>
           <t>job_report_monthly</t>
         </is>
@@ -14015,7 +14125,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -14025,12 +14135,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -14045,12 +14155,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -14060,12 +14170,12 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -14075,7 +14185,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -14085,7 +14195,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -14105,7 +14215,7 @@
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -14115,27 +14225,27 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -14170,7 +14280,7 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
@@ -14180,7 +14290,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -14205,22 +14315,22 @@
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -14260,12 +14370,12 @@
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
@@ -14280,12 +14390,12 @@
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BF23" t="inlineStr">
@@ -14300,12 +14410,12 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BJ23" t="inlineStr">
@@ -14330,7 +14440,7 @@
       </c>
       <c r="BN23" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BO23" t="inlineStr">
@@ -14340,7 +14450,7 @@
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
@@ -14365,12 +14475,12 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -14380,7 +14490,7 @@
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
@@ -14390,7 +14500,7 @@
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -14425,12 +14535,12 @@
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CI23" t="inlineStr">
@@ -14440,12 +14550,12 @@
       </c>
       <c r="CJ23" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CK23" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CL23" t="inlineStr">
@@ -14495,7 +14605,7 @@
       </c>
       <c r="CU23" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CV23" t="inlineStr">
@@ -14505,12 +14615,12 @@
       </c>
       <c r="CW23" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CX23" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CY23" t="inlineStr">
@@ -14530,7 +14640,7 @@
       </c>
       <c r="DB23" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DC23" t="inlineStr">
@@ -14540,7 +14650,7 @@
       </c>
       <c r="DD23" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DE23" t="inlineStr">
@@ -14550,27 +14660,27 @@
       </c>
       <c r="DF23" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DG23" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DH23" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DI23" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DJ23" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DK23" t="inlineStr">
@@ -14580,22 +14690,22 @@
       </c>
       <c r="DL23" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DM23" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DN23" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DO23" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DP23" t="inlineStr">
@@ -14605,15 +14715,20 @@
       </c>
       <c r="DQ23" t="inlineStr">
         <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="DR23" t="inlineStr">
+        <is>
           <t>finance</t>
         </is>
       </c>
-      <c r="DR23" t="inlineStr">
+      <c r="DS23" t="inlineStr">
         <is>
           <t>billing</t>
         </is>
       </c>
-      <c r="DS23" t="inlineStr">
+      <c r="DT23" t="inlineStr">
         <is>
           <t>job_payment_proc</t>
         </is>
@@ -14647,12 +14762,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -14662,12 +14777,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -14677,12 +14792,12 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -14742,12 +14857,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -14757,12 +14872,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
@@ -14792,12 +14907,12 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -14827,17 +14942,17 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
@@ -14847,7 +14962,7 @@
       </c>
       <c r="AT24" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AU24" t="inlineStr">
@@ -14872,7 +14987,7 @@
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AZ24" t="inlineStr">
@@ -14887,17 +15002,17 @@
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BD24" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BE24" t="inlineStr">
@@ -14917,7 +15032,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BI24" t="inlineStr">
@@ -14932,7 +15047,7 @@
       </c>
       <c r="BK24" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BL24" t="inlineStr">
@@ -14947,12 +15062,12 @@
       </c>
       <c r="BN24" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BO24" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BP24" t="inlineStr">
@@ -14977,12 +15092,12 @@
       </c>
       <c r="BT24" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BU24" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BV24" t="inlineStr">
@@ -15082,22 +15197,22 @@
       </c>
       <c r="CO24" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CP24" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CQ24" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CR24" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CS24" t="inlineStr">
@@ -15112,12 +15227,12 @@
       </c>
       <c r="CU24" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CV24" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CW24" t="inlineStr">
@@ -15142,22 +15257,22 @@
       </c>
       <c r="DA24" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DB24" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DC24" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DD24" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DE24" t="inlineStr">
@@ -15172,22 +15287,22 @@
       </c>
       <c r="DG24" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DH24" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DI24" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DJ24" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DK24" t="inlineStr">
@@ -15197,22 +15312,22 @@
       </c>
       <c r="DL24" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DM24" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DN24" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DO24" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DP24" t="inlineStr">
@@ -15222,15 +15337,20 @@
       </c>
       <c r="DQ24" t="inlineStr">
         <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="DR24" t="inlineStr">
+        <is>
           <t>finance</t>
         </is>
       </c>
-      <c r="DR24" t="inlineStr">
+      <c r="DS24" t="inlineStr">
         <is>
           <t>billing</t>
         </is>
       </c>
-      <c r="DS24" t="inlineStr">
+      <c r="DT24" t="inlineStr">
         <is>
           <t>job_tax_calc</t>
         </is>
@@ -15244,7 +15364,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -15264,17 +15384,17 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -15339,12 +15459,12 @@
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
@@ -15364,12 +15484,12 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
@@ -15379,7 +15499,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
@@ -15389,7 +15509,7 @@
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
@@ -15419,12 +15539,12 @@
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
@@ -15489,12 +15609,12 @@
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BA25" t="inlineStr">
@@ -15509,17 +15629,17 @@
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BD25" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BF25" t="inlineStr">
@@ -15529,7 +15649,7 @@
       </c>
       <c r="BG25" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BH25" t="inlineStr">
@@ -15554,7 +15674,7 @@
       </c>
       <c r="BL25" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BM25" t="inlineStr">
@@ -15564,7 +15684,7 @@
       </c>
       <c r="BN25" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BO25" t="inlineStr">
@@ -15589,22 +15709,22 @@
       </c>
       <c r="BS25" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BT25" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BU25" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="BV25" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="BW25" t="inlineStr">
@@ -15634,12 +15754,12 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CC25" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CD25" t="inlineStr">
@@ -15649,12 +15769,12 @@
       </c>
       <c r="CE25" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CF25" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CG25" t="inlineStr">
@@ -15679,17 +15799,17 @@
       </c>
       <c r="CK25" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CL25" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CM25" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CN25" t="inlineStr">
@@ -15699,7 +15819,7 @@
       </c>
       <c r="CO25" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CP25" t="inlineStr">
@@ -15724,12 +15844,12 @@
       </c>
       <c r="CT25" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CU25" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CV25" t="inlineStr">
@@ -15739,52 +15859,52 @@
       </c>
       <c r="CW25" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CX25" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="CY25" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="CZ25" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DA25" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DB25" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DC25" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DD25" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DE25" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DF25" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DG25" t="inlineStr">
@@ -15794,12 +15914,12 @@
       </c>
       <c r="DH25" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DI25" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DJ25" t="inlineStr">
@@ -15814,7 +15934,7 @@
       </c>
       <c r="DL25" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="DM25" t="inlineStr">
@@ -15824,7 +15944,7 @@
       </c>
       <c r="DN25" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>error</t>
         </is>
       </c>
       <c r="DO25" t="inlineStr">
@@ -15839,15 +15959,20 @@
       </c>
       <c r="DQ25" t="inlineStr">
         <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="DR25" t="inlineStr">
+        <is>
           <t>finance</t>
         </is>
       </c>
-      <c r="DR25" t="inlineStr">
+      <c r="DS25" t="inlineStr">
         <is>
           <t>billing</t>
         </is>
       </c>
-      <c r="DS25" t="inlineStr">
+      <c r="DT25" t="inlineStr">
         <is>
           <t>job_invoice_gen</t>
         </is>
